--- a/Data/Raw/Hach/B2ONutrientData.xlsx
+++ b/Data/Raw/Hach/B2ONutrientData.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28005"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28706"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="6181" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9D85C27-6838-4EFF-86C8-79485D424EA5}"/>
+  <xr:revisionPtr revIDLastSave="7729" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA8F7657-A165-458C-970C-708C04A69046}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2166" uniqueCount="270">
   <si>
     <t>Date</t>
   </si>
@@ -458,13 +458,154 @@
     <t>Calcium: 302</t>
   </si>
   <si>
+    <t>CS, SS</t>
+  </si>
+  <si>
+    <t>Calcium: 357 (NOTE: No pH probe, alakalinity is based on color)</t>
+  </si>
+  <si>
+    <t>Calcium: 338 (NOTE: No pH probe, alakalinity is based on color)</t>
+  </si>
+  <si>
+    <t>NOTE: No pH probe, alakalinity is based on color</t>
+  </si>
+  <si>
+    <t>SS, CS</t>
+  </si>
+  <si>
+    <t>Calcium: 361</t>
+  </si>
+  <si>
+    <t>Calcium: 386 NOTE: No pH probe, alakalinity is based on color</t>
+  </si>
+  <si>
+    <t>SS,CS</t>
+  </si>
+  <si>
+    <t>Calcium: 356 NOTE: No pH probe, alakalinity is based on color</t>
+  </si>
+  <si>
+    <t>SE,CS</t>
+  </si>
+  <si>
+    <t>NOTE: No pH prob, alkalinity Based on color</t>
+  </si>
+  <si>
+    <t>SE, CS</t>
+  </si>
+  <si>
+    <t>NOTE: No pH probe, alkalinity Based on color</t>
+  </si>
+  <si>
+    <t>NOTE: No Calcium because no more powder packets,  No pH probe, alkalinity Based on color</t>
+  </si>
+  <si>
+    <t>SS</t>
+  </si>
+  <si>
+    <t>NOTE: No pH probe, alkalinity based on color</t>
+  </si>
+  <si>
+    <t>NOTE: No Calcium because no more powder packets, No pH probe, alkalinity Based on color</t>
+  </si>
+  <si>
+    <t>NOTE: pH probe came too late for accurate readings</t>
+  </si>
+  <si>
+    <t>NOTE: No calcium because no more powder packets</t>
+  </si>
+  <si>
+    <t>Mangrove</t>
+  </si>
+  <si>
+    <t>Calcium: 357, Note: Alk based on color</t>
+  </si>
+  <si>
+    <t>Calcium: 369, Note: Alk based on color</t>
+  </si>
+  <si>
+    <t>Calcium: 360 NOTE: No pH probe, alkalinity based on color</t>
+  </si>
+  <si>
+    <t>SJE. CS</t>
+  </si>
+  <si>
+    <t>pH probe working normal</t>
+  </si>
+  <si>
+    <t>SJE, Cs</t>
+  </si>
+  <si>
+    <t>Calcium: 343</t>
+  </si>
+  <si>
+    <t>Calcium: 376</t>
+  </si>
+  <si>
+    <t>CM, CS,SJE</t>
+  </si>
+  <si>
+    <t>CM, CS, SJE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calcium: 325  </t>
+  </si>
+  <si>
+    <t>Calcium: 269 NOTE: calcium substrate in mix tank --&gt; milkiness in R2, everything turned off</t>
+  </si>
+  <si>
+    <t>CS, CM, SJE</t>
+  </si>
+  <si>
+    <t>Calcium: 325</t>
+  </si>
+  <si>
+    <t>Calcium: 290</t>
+  </si>
+  <si>
+    <t>CM. CS</t>
+  </si>
+  <si>
+    <t>Calcium: 317</t>
+  </si>
+  <si>
+    <t>Calcium: 358</t>
+  </si>
+  <si>
+    <t>+ ++</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CM, CS, SS, </t>
+  </si>
+  <si>
+    <t>collected sample at the shore.</t>
+  </si>
+  <si>
+    <t>CM, CS, SS</t>
+  </si>
+  <si>
+    <t>Calcium: 331</t>
+  </si>
+  <si>
+    <t>Calcium: 373</t>
+  </si>
+  <si>
+    <t>Calcium: 372</t>
+  </si>
+  <si>
+    <t>Calcium: 392</t>
+  </si>
+  <si>
+    <t>Calcium: 328</t>
+  </si>
+  <si>
+    <t>Calcium: 401</t>
+  </si>
+  <si>
     <t>ORP</t>
   </si>
   <si>
     <t>Units for nutrients are mg/L, ORP is measured in mV</t>
-  </si>
-  <si>
-    <t>Mangrove</t>
   </si>
   <si>
     <t xml:space="preserve"> KL</t>
@@ -717,7 +858,7 @@
     <numFmt numFmtId="166" formatCode="0.000"/>
     <numFmt numFmtId="167" formatCode="mm/dd/yy;@"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -755,6 +896,25 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -905,7 +1065,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -988,6 +1148,17 @@
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1302,7 +1473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6EB9ACE-4815-4899-AD47-5981DDC52F20}">
-  <dimension ref="A1:N525"/>
+  <dimension ref="A1:N661"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.140625" style="61" customWidth="1"/>
@@ -1317,7 +1488,7 @@
     <col min="10" max="10" width="9.140625" style="30"/>
     <col min="11" max="11" width="9.140625" style="25"/>
     <col min="12" max="12" width="16.85546875" customWidth="1"/>
-    <col min="13" max="13" width="72.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="79.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -17550,10 +17721,4365 @@
         <v>34</v>
       </c>
     </row>
+    <row r="526" spans="1:13">
+      <c r="A526" s="61">
+        <v>45544</v>
+      </c>
+      <c r="B526" t="s">
+        <v>17</v>
+      </c>
+      <c r="C526" s="35">
+        <v>0</v>
+      </c>
+      <c r="D526" s="25">
+        <v>0.06</v>
+      </c>
+      <c r="E526" s="26">
+        <v>1.7</v>
+      </c>
+      <c r="F526" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="H526" s="35">
+        <v>131</v>
+      </c>
+      <c r="K526" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L526" t="s">
+        <v>140</v>
+      </c>
+      <c r="M526" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="527" spans="1:13">
+      <c r="A527" s="61">
+        <v>45544</v>
+      </c>
+      <c r="B527" t="s">
+        <v>18</v>
+      </c>
+      <c r="C527" s="35">
+        <v>0</v>
+      </c>
+      <c r="D527" s="25">
+        <v>0.3</v>
+      </c>
+      <c r="E527" s="26">
+        <v>1.8</v>
+      </c>
+      <c r="F527" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="H527" s="35">
+        <v>95</v>
+      </c>
+      <c r="K527" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L527" t="s">
+        <v>140</v>
+      </c>
+      <c r="M527" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="528" spans="1:13">
+      <c r="A528" s="61">
+        <v>45548</v>
+      </c>
+      <c r="B528" t="s">
+        <v>13</v>
+      </c>
+      <c r="C528" s="35">
+        <v>0</v>
+      </c>
+      <c r="D528" s="25">
+        <v>0</v>
+      </c>
+      <c r="E528" s="26">
+        <v>1.5</v>
+      </c>
+      <c r="F528" s="26">
+        <v>2.8</v>
+      </c>
+      <c r="H528" s="35">
+        <v>116</v>
+      </c>
+      <c r="I528" s="25">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="J528" s="30">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="L528" t="s">
+        <v>99</v>
+      </c>
+      <c r="M528" s="16" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="529" spans="1:13">
+      <c r="A529" s="61">
+        <v>45548</v>
+      </c>
+      <c r="B529" t="s">
+        <v>16</v>
+      </c>
+      <c r="C529" s="35">
+        <v>5</v>
+      </c>
+      <c r="D529" s="25">
+        <v>0.39</v>
+      </c>
+      <c r="E529" s="26">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F529" s="26">
+        <v>3.6</v>
+      </c>
+      <c r="L529" t="s">
+        <v>99</v>
+      </c>
+      <c r="M529" s="16" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="530" spans="1:13">
+      <c r="A530" s="61">
+        <v>45548</v>
+      </c>
+      <c r="B530" t="s">
+        <v>17</v>
+      </c>
+      <c r="C530" s="35">
+        <v>0</v>
+      </c>
+      <c r="D530" s="25">
+        <v>0.45</v>
+      </c>
+      <c r="E530" s="26">
+        <v>1.5</v>
+      </c>
+      <c r="F530" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="H530" s="35">
+        <v>100</v>
+      </c>
+      <c r="I530" s="25">
+        <v>0.23</v>
+      </c>
+      <c r="J530" s="30">
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="L530" t="s">
+        <v>99</v>
+      </c>
+      <c r="M530" s="16" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="531" spans="1:13">
+      <c r="A531" s="61">
+        <v>45548</v>
+      </c>
+      <c r="B531" t="s">
+        <v>18</v>
+      </c>
+      <c r="C531" s="35">
+        <v>0</v>
+      </c>
+      <c r="D531" s="25">
+        <v>0.05</v>
+      </c>
+      <c r="E531" s="26">
+        <v>1.9</v>
+      </c>
+      <c r="F531" s="26">
+        <v>3.2</v>
+      </c>
+      <c r="H531" s="35">
+        <v>97</v>
+      </c>
+      <c r="I531" s="25">
+        <v>0.12</v>
+      </c>
+      <c r="J531" s="30">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="L531" t="s">
+        <v>99</v>
+      </c>
+      <c r="M531" s="16" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="532" spans="1:13">
+      <c r="A532" s="61">
+        <v>45551</v>
+      </c>
+      <c r="B532" t="s">
+        <v>17</v>
+      </c>
+      <c r="C532" s="35">
+        <v>0</v>
+      </c>
+      <c r="D532" s="25">
+        <v>0.05</v>
+      </c>
+      <c r="E532" s="26">
+        <v>1.5</v>
+      </c>
+      <c r="F532" s="26">
+        <v>1.7</v>
+      </c>
+      <c r="H532" s="35">
+        <v>113</v>
+      </c>
+      <c r="K532" s="25">
+        <v>0</v>
+      </c>
+      <c r="L532" t="s">
+        <v>144</v>
+      </c>
+      <c r="M532" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="533" spans="1:13">
+      <c r="A533" s="61">
+        <v>45551</v>
+      </c>
+      <c r="B533" t="s">
+        <v>18</v>
+      </c>
+      <c r="C533" s="35">
+        <v>0</v>
+      </c>
+      <c r="D533" s="25">
+        <v>0.06</v>
+      </c>
+      <c r="E533" s="26">
+        <v>1.2</v>
+      </c>
+      <c r="F533" s="26">
+        <v>1.6</v>
+      </c>
+      <c r="H533" s="35">
+        <v>96</v>
+      </c>
+      <c r="K533" s="25">
+        <v>0</v>
+      </c>
+      <c r="L533" t="s">
+        <v>144</v>
+      </c>
+      <c r="M533" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="534" spans="1:13">
+      <c r="A534" s="61">
+        <v>45555</v>
+      </c>
+      <c r="B534" t="s">
+        <v>13</v>
+      </c>
+      <c r="C534" s="35">
+        <v>0</v>
+      </c>
+      <c r="D534" s="25">
+        <v>0.03</v>
+      </c>
+      <c r="E534" s="26">
+        <v>1.53</v>
+      </c>
+      <c r="F534" s="26">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="H534" s="35">
+        <v>127</v>
+      </c>
+      <c r="I534" s="25">
+        <v>0.86</v>
+      </c>
+      <c r="J534" s="30">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="L534" t="s">
+        <v>103</v>
+      </c>
+      <c r="M534" s="16" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="535" spans="1:13">
+      <c r="A535" s="61">
+        <v>45555</v>
+      </c>
+      <c r="B535" t="s">
+        <v>16</v>
+      </c>
+      <c r="C535" s="35">
+        <v>18</v>
+      </c>
+      <c r="D535" s="25">
+        <v>0.27</v>
+      </c>
+      <c r="E535" s="26">
+        <v>1.37</v>
+      </c>
+      <c r="F535" s="26">
+        <v>1.77</v>
+      </c>
+      <c r="L535" t="s">
+        <v>103</v>
+      </c>
+      <c r="M535" s="16" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="536" spans="1:13">
+      <c r="A536" s="61">
+        <v>45555</v>
+      </c>
+      <c r="B536" t="s">
+        <v>17</v>
+      </c>
+      <c r="C536" s="35">
+        <v>0</v>
+      </c>
+      <c r="D536" s="25">
+        <v>0.01</v>
+      </c>
+      <c r="E536" s="26">
+        <v>1.3</v>
+      </c>
+      <c r="F536" s="26">
+        <v>2.1</v>
+      </c>
+      <c r="H536" s="35">
+        <v>112</v>
+      </c>
+      <c r="I536" s="25">
+        <v>0.23</v>
+      </c>
+      <c r="J536" s="30">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="L536" t="s">
+        <v>103</v>
+      </c>
+      <c r="M536" s="16" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="537" spans="1:13">
+      <c r="A537" s="61">
+        <v>45555</v>
+      </c>
+      <c r="B537" t="s">
+        <v>18</v>
+      </c>
+      <c r="C537" s="35">
+        <v>0</v>
+      </c>
+      <c r="D537" s="25">
+        <v>0.03</v>
+      </c>
+      <c r="E537" s="26">
+        <v>1.43</v>
+      </c>
+      <c r="F537" s="26">
+        <v>1.97</v>
+      </c>
+      <c r="H537" s="35">
+        <v>93</v>
+      </c>
+      <c r="I537" s="25">
+        <v>0.1</v>
+      </c>
+      <c r="J537" s="30">
+        <v>0.01</v>
+      </c>
+      <c r="L537" t="s">
+        <v>103</v>
+      </c>
+      <c r="M537" s="16" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="538" spans="1:13">
+      <c r="A538" s="61">
+        <v>45558</v>
+      </c>
+      <c r="B538" t="s">
+        <v>17</v>
+      </c>
+      <c r="C538" s="35">
+        <v>0</v>
+      </c>
+      <c r="D538" s="25">
+        <v>0.09</v>
+      </c>
+      <c r="E538" s="26">
+        <v>1.63</v>
+      </c>
+      <c r="F538" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="H538" s="35">
+        <v>180</v>
+      </c>
+      <c r="K538" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L538" t="s">
+        <v>144</v>
+      </c>
+      <c r="M538" s="16" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="539" spans="1:13">
+      <c r="A539" s="61">
+        <v>45558</v>
+      </c>
+      <c r="B539" t="s">
+        <v>18</v>
+      </c>
+      <c r="C539" s="35">
+        <v>0</v>
+      </c>
+      <c r="D539" s="25">
+        <v>0.04</v>
+      </c>
+      <c r="E539" s="26">
+        <v>1.5</v>
+      </c>
+      <c r="F539" s="26">
+        <v>2.1</v>
+      </c>
+      <c r="H539" s="35">
+        <v>190</v>
+      </c>
+      <c r="K539" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L539" t="s">
+        <v>147</v>
+      </c>
+      <c r="M539" s="16" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="540" spans="1:13">
+      <c r="A540" s="61">
+        <v>45562</v>
+      </c>
+      <c r="B540" t="s">
+        <v>13</v>
+      </c>
+      <c r="C540" s="35">
+        <v>0</v>
+      </c>
+      <c r="D540" s="25">
+        <v>0.2</v>
+      </c>
+      <c r="E540" s="26">
+        <v>1.7</v>
+      </c>
+      <c r="F540" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="H540" s="35">
+        <v>111</v>
+      </c>
+      <c r="I540" s="25">
+        <v>0.72599999999999998</v>
+      </c>
+      <c r="J540" s="30">
+        <v>3.1E-2</v>
+      </c>
+      <c r="L540" t="s">
+        <v>149</v>
+      </c>
+      <c r="M540" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="541" spans="1:13">
+      <c r="A541" s="61">
+        <v>45562</v>
+      </c>
+      <c r="B541" t="s">
+        <v>16</v>
+      </c>
+      <c r="C541" s="35">
+        <v>17</v>
+      </c>
+      <c r="D541" s="25">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="E541" s="26">
+        <v>1.5</v>
+      </c>
+      <c r="F541" s="26">
+        <v>1.5</v>
+      </c>
+      <c r="L541" t="s">
+        <v>151</v>
+      </c>
+      <c r="M541" s="71" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="542" spans="1:13">
+      <c r="A542" s="61">
+        <v>45562</v>
+      </c>
+      <c r="B542" t="s">
+        <v>17</v>
+      </c>
+      <c r="C542" s="35">
+        <v>0</v>
+      </c>
+      <c r="D542" s="25">
+        <v>0.04</v>
+      </c>
+      <c r="E542" s="26">
+        <v>1.3</v>
+      </c>
+      <c r="F542" s="26">
+        <v>2</v>
+      </c>
+      <c r="H542" s="35">
+        <v>116</v>
+      </c>
+      <c r="I542" s="25">
+        <v>0.17</v>
+      </c>
+      <c r="J542" s="30">
+        <v>0.03</v>
+      </c>
+      <c r="L542" t="s">
+        <v>149</v>
+      </c>
+      <c r="M542" s="71" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="543" spans="1:13">
+      <c r="A543" s="61">
+        <v>45562</v>
+      </c>
+      <c r="B543" t="s">
+        <v>18</v>
+      </c>
+      <c r="C543" s="35">
+        <v>0</v>
+      </c>
+      <c r="D543" s="25">
+        <v>0</v>
+      </c>
+      <c r="E543" s="26">
+        <v>1.3</v>
+      </c>
+      <c r="F543" s="26">
+        <v>1.8</v>
+      </c>
+      <c r="H543" s="35">
+        <v>94</v>
+      </c>
+      <c r="I543" s="25">
+        <v>0.17299999999999999</v>
+      </c>
+      <c r="J543" s="30">
+        <v>1.6E-2</v>
+      </c>
+      <c r="L543" t="s">
+        <v>149</v>
+      </c>
+      <c r="M543" s="71" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="544" spans="1:13">
+      <c r="A544" s="61">
+        <v>45565</v>
+      </c>
+      <c r="B544" t="s">
+        <v>17</v>
+      </c>
+      <c r="C544" s="35">
+        <v>0</v>
+      </c>
+      <c r="D544" s="25">
+        <v>0.17</v>
+      </c>
+      <c r="E544" s="26">
+        <v>1.4</v>
+      </c>
+      <c r="F544" s="26">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="H544" s="35">
+        <v>100</v>
+      </c>
+      <c r="K544" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L544" t="s">
+        <v>144</v>
+      </c>
+      <c r="M544" s="16" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="545" spans="1:13">
+      <c r="A545" s="61">
+        <v>45565</v>
+      </c>
+      <c r="B545" t="s">
+        <v>18</v>
+      </c>
+      <c r="C545" s="35">
+        <v>0</v>
+      </c>
+      <c r="D545" s="25">
+        <v>0.11</v>
+      </c>
+      <c r="E545" s="26">
+        <v>1.5</v>
+      </c>
+      <c r="F545" s="26">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="H545" s="35">
+        <v>151</v>
+      </c>
+      <c r="K545" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L545" t="s">
+        <v>144</v>
+      </c>
+      <c r="M545" s="16" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="546" spans="1:13">
+      <c r="A546" s="61">
+        <v>45569</v>
+      </c>
+      <c r="B546" t="s">
+        <v>13</v>
+      </c>
+      <c r="C546" s="35">
+        <v>0</v>
+      </c>
+      <c r="D546" s="25">
+        <v>0.12</v>
+      </c>
+      <c r="E546" s="26">
+        <v>1.7</v>
+      </c>
+      <c r="F546" s="26">
+        <v>2.7</v>
+      </c>
+      <c r="H546" s="35">
+        <v>127</v>
+      </c>
+      <c r="I546" s="25">
+        <v>0.81</v>
+      </c>
+      <c r="J546" s="30">
+        <v>0.06</v>
+      </c>
+      <c r="L546" t="s">
+        <v>34</v>
+      </c>
+      <c r="M546" s="16" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="547" spans="1:13">
+      <c r="A547" s="61">
+        <v>45569</v>
+      </c>
+      <c r="B547" t="s">
+        <v>16</v>
+      </c>
+      <c r="C547" s="35">
+        <v>14</v>
+      </c>
+      <c r="D547" s="25">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="E547" s="26">
+        <v>1.2</v>
+      </c>
+      <c r="F547" s="26">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="L547" t="s">
+        <v>34</v>
+      </c>
+      <c r="M547" s="16" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="548" spans="1:13">
+      <c r="A548" s="61">
+        <v>45569</v>
+      </c>
+      <c r="B548" t="s">
+        <v>17</v>
+      </c>
+      <c r="C548" s="35">
+        <v>0</v>
+      </c>
+      <c r="D548" s="25">
+        <v>0</v>
+      </c>
+      <c r="E548" s="26">
+        <v>1.4</v>
+      </c>
+      <c r="F548" s="26">
+        <v>2.1</v>
+      </c>
+      <c r="H548" s="35">
+        <v>127</v>
+      </c>
+      <c r="I548" s="25">
+        <v>0.23</v>
+      </c>
+      <c r="J548" s="30">
+        <v>0</v>
+      </c>
+      <c r="L548" t="s">
+        <v>34</v>
+      </c>
+      <c r="M548" s="16" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="549" spans="1:13">
+      <c r="A549" s="61">
+        <v>45569</v>
+      </c>
+      <c r="B549" t="s">
+        <v>18</v>
+      </c>
+      <c r="C549" s="35">
+        <v>0</v>
+      </c>
+      <c r="D549" s="25">
+        <v>0</v>
+      </c>
+      <c r="E549" s="26">
+        <v>1.5</v>
+      </c>
+      <c r="F549" s="26">
+        <v>2.1</v>
+      </c>
+      <c r="H549" s="35">
+        <v>90</v>
+      </c>
+      <c r="I549" s="25">
+        <v>0.2</v>
+      </c>
+      <c r="J549" s="30">
+        <v>1.4E-2</v>
+      </c>
+      <c r="L549" t="s">
+        <v>34</v>
+      </c>
+      <c r="M549" s="16" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="550" spans="1:13">
+      <c r="A550" s="61">
+        <v>45572</v>
+      </c>
+      <c r="B550" t="s">
+        <v>17</v>
+      </c>
+      <c r="C550" s="35">
+        <v>0</v>
+      </c>
+      <c r="D550" s="25">
+        <v>0.09</v>
+      </c>
+      <c r="E550" s="26">
+        <v>1.3</v>
+      </c>
+      <c r="F550" s="26">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="H550" s="35">
+        <v>125</v>
+      </c>
+      <c r="K550" s="25">
+        <v>0</v>
+      </c>
+      <c r="L550" t="s">
+        <v>124</v>
+      </c>
+      <c r="M550" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="551" spans="1:13">
+      <c r="A551" s="61">
+        <v>45572</v>
+      </c>
+      <c r="B551" t="s">
+        <v>18</v>
+      </c>
+      <c r="C551" s="35">
+        <v>0</v>
+      </c>
+      <c r="D551" s="25">
+        <v>0.03</v>
+      </c>
+      <c r="E551" s="26">
+        <v>1.26</v>
+      </c>
+      <c r="F551" s="26">
+        <v>2.1</v>
+      </c>
+      <c r="H551" s="35">
+        <v>82</v>
+      </c>
+      <c r="K551" s="25">
+        <v>0</v>
+      </c>
+      <c r="L551" t="s">
+        <v>124</v>
+      </c>
+      <c r="M551" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="552" spans="1:13">
+      <c r="A552" s="61">
+        <v>45576</v>
+      </c>
+      <c r="B552" t="s">
+        <v>13</v>
+      </c>
+      <c r="C552" s="35">
+        <v>0</v>
+      </c>
+      <c r="D552" s="25">
+        <v>0.02</v>
+      </c>
+      <c r="E552" s="26">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F552" s="26">
+        <v>1.3</v>
+      </c>
+      <c r="H552" s="35">
+        <v>128</v>
+      </c>
+      <c r="I552" s="25">
+        <v>0.81299999999999994</v>
+      </c>
+      <c r="J552" s="30">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="L552" t="s">
+        <v>99</v>
+      </c>
+      <c r="M552" s="16" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="553" spans="1:13">
+      <c r="A553" s="61">
+        <v>45576</v>
+      </c>
+      <c r="B553" t="s">
+        <v>16</v>
+      </c>
+      <c r="C553" s="35">
+        <v>15</v>
+      </c>
+      <c r="D553" s="25">
+        <v>0.43</v>
+      </c>
+      <c r="E553" s="26">
+        <v>1.9</v>
+      </c>
+      <c r="F553" s="26">
+        <v>2.1</v>
+      </c>
+      <c r="L553" t="s">
+        <v>99</v>
+      </c>
+      <c r="M553" s="16" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="554" spans="1:13">
+      <c r="A554" s="61">
+        <v>45576</v>
+      </c>
+      <c r="B554" t="s">
+        <v>17</v>
+      </c>
+      <c r="C554" s="35">
+        <v>0</v>
+      </c>
+      <c r="D554" s="25">
+        <v>0.02</v>
+      </c>
+      <c r="E554" s="26">
+        <v>1.6</v>
+      </c>
+      <c r="F554" s="26">
+        <v>1.8</v>
+      </c>
+      <c r="H554" s="35">
+        <v>103</v>
+      </c>
+      <c r="I554" s="25">
+        <v>0.1777</v>
+      </c>
+      <c r="J554" s="30">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="L554" t="s">
+        <v>99</v>
+      </c>
+      <c r="M554" s="16" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="555" spans="1:13">
+      <c r="A555" s="61">
+        <v>45576</v>
+      </c>
+      <c r="B555" t="s">
+        <v>18</v>
+      </c>
+      <c r="C555" s="35">
+        <v>0</v>
+      </c>
+      <c r="D555" s="25">
+        <v>0.08</v>
+      </c>
+      <c r="E555" s="26">
+        <v>1.5</v>
+      </c>
+      <c r="F555" s="26">
+        <v>1.7</v>
+      </c>
+      <c r="H555" s="35">
+        <v>81</v>
+      </c>
+      <c r="I555" s="25">
+        <v>0.19</v>
+      </c>
+      <c r="J555" s="30">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="L555" t="s">
+        <v>99</v>
+      </c>
+      <c r="M555" s="16" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="556" spans="1:13">
+      <c r="A556" s="61">
+        <v>45579</v>
+      </c>
+      <c r="B556" t="s">
+        <v>17</v>
+      </c>
+      <c r="C556" s="35">
+        <v>0</v>
+      </c>
+      <c r="D556" s="25">
+        <v>0.04</v>
+      </c>
+      <c r="E556" s="26">
+        <v>1.5</v>
+      </c>
+      <c r="F556" s="26">
+        <v>2.1</v>
+      </c>
+      <c r="H556" s="35">
+        <v>153</v>
+      </c>
+      <c r="K556" s="25">
+        <v>0.06</v>
+      </c>
+      <c r="L556" t="s">
+        <v>154</v>
+      </c>
+      <c r="M556" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="557" spans="1:13">
+      <c r="A557" s="61">
+        <v>45579</v>
+      </c>
+      <c r="B557" t="s">
+        <v>18</v>
+      </c>
+      <c r="C557" s="35">
+        <v>1</v>
+      </c>
+      <c r="D557" s="25">
+        <v>0.02</v>
+      </c>
+      <c r="E557" s="26">
+        <v>1.33</v>
+      </c>
+      <c r="F557" s="26">
+        <v>2</v>
+      </c>
+      <c r="H557" s="35">
+        <v>96</v>
+      </c>
+      <c r="K557" s="25">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="L557" t="s">
+        <v>154</v>
+      </c>
+      <c r="M557" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="558" spans="1:13">
+      <c r="A558" s="61">
+        <v>45583</v>
+      </c>
+      <c r="B558" t="s">
+        <v>13</v>
+      </c>
+      <c r="C558" s="35">
+        <v>0</v>
+      </c>
+      <c r="D558" s="25">
+        <v>0.21</v>
+      </c>
+      <c r="E558" s="26">
+        <v>1</v>
+      </c>
+      <c r="F558" s="26">
+        <v>1.63</v>
+      </c>
+      <c r="H558" s="35">
+        <v>121</v>
+      </c>
+      <c r="I558" s="25">
+        <v>0.82</v>
+      </c>
+      <c r="J558" s="30">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="L558" t="s">
+        <v>114</v>
+      </c>
+      <c r="M558" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="559" spans="1:13">
+      <c r="A559" s="61">
+        <v>45583</v>
+      </c>
+      <c r="B559" t="s">
+        <v>16</v>
+      </c>
+      <c r="C559" s="35">
+        <v>17</v>
+      </c>
+      <c r="D559" s="25">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="E559" s="26">
+        <v>1.8</v>
+      </c>
+      <c r="F559" s="26">
+        <v>1.87</v>
+      </c>
+      <c r="L559" t="s">
+        <v>114</v>
+      </c>
+      <c r="M559" s="71" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="560" spans="1:13">
+      <c r="A560" s="61">
+        <v>45583</v>
+      </c>
+      <c r="B560" t="s">
+        <v>17</v>
+      </c>
+      <c r="C560" s="35">
+        <v>0</v>
+      </c>
+      <c r="D560" s="25">
+        <v>0.04</v>
+      </c>
+      <c r="E560" s="26">
+        <v>1.57</v>
+      </c>
+      <c r="F560" s="26">
+        <v>2.5299999999999998</v>
+      </c>
+      <c r="H560" s="35">
+        <v>114</v>
+      </c>
+      <c r="I560" s="25">
+        <v>0.24</v>
+      </c>
+      <c r="J560" s="30">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="L560" t="s">
+        <v>114</v>
+      </c>
+      <c r="M560" s="71" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="561" spans="1:13">
+      <c r="A561" s="61">
+        <v>45583</v>
+      </c>
+      <c r="B561" t="s">
+        <v>18</v>
+      </c>
+      <c r="C561" s="35">
+        <v>0</v>
+      </c>
+      <c r="D561" s="25">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="E561" s="26">
+        <v>1.3</v>
+      </c>
+      <c r="F561" s="26">
+        <v>1.7</v>
+      </c>
+      <c r="H561" s="35">
+        <v>90</v>
+      </c>
+      <c r="I561" s="25">
+        <v>1.17</v>
+      </c>
+      <c r="J561" s="30">
+        <v>0.11799999999999999</v>
+      </c>
+      <c r="L561" t="s">
+        <v>114</v>
+      </c>
+      <c r="M561" s="71" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="562" spans="1:13">
+      <c r="A562" s="61">
+        <v>45586</v>
+      </c>
+      <c r="B562" t="s">
+        <v>17</v>
+      </c>
+      <c r="C562" s="35">
+        <v>0</v>
+      </c>
+      <c r="D562" s="25">
+        <v>0.01</v>
+      </c>
+      <c r="E562" s="26">
+        <v>2</v>
+      </c>
+      <c r="F562" s="26">
+        <v>2.7</v>
+      </c>
+      <c r="H562" s="35">
+        <v>126</v>
+      </c>
+      <c r="K562" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L562" t="s">
+        <v>34</v>
+      </c>
+      <c r="M562" s="16" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="563" spans="1:13">
+      <c r="A563" s="61">
+        <v>45586</v>
+      </c>
+      <c r="B563" t="s">
+        <v>18</v>
+      </c>
+      <c r="C563" s="35">
+        <v>0</v>
+      </c>
+      <c r="D563" s="25">
+        <v>0</v>
+      </c>
+      <c r="E563" s="26">
+        <v>1.7</v>
+      </c>
+      <c r="F563" s="26">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="H563" s="35">
+        <v>88</v>
+      </c>
+      <c r="K563" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L563" t="s">
+        <v>34</v>
+      </c>
+      <c r="M563" s="16" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="564" spans="1:13">
+      <c r="A564" s="61">
+        <v>45590</v>
+      </c>
+      <c r="B564" t="s">
+        <v>13</v>
+      </c>
+      <c r="C564" s="35">
+        <v>0</v>
+      </c>
+      <c r="D564" s="25">
+        <v>0</v>
+      </c>
+      <c r="E564" s="26">
+        <v>1.3</v>
+      </c>
+      <c r="F564" s="26">
+        <v>0.8</v>
+      </c>
+      <c r="H564" s="35">
+        <v>122</v>
+      </c>
+      <c r="I564" s="25">
+        <v>0.90300000000000002</v>
+      </c>
+      <c r="J564" s="30">
+        <v>3.2300000000000002E-2</v>
+      </c>
+      <c r="L564" t="s">
+        <v>103</v>
+      </c>
+      <c r="M564" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="565" spans="1:13">
+      <c r="A565" s="61">
+        <v>45590</v>
+      </c>
+      <c r="B565" t="s">
+        <v>16</v>
+      </c>
+      <c r="C565" s="35">
+        <v>14</v>
+      </c>
+      <c r="D565" s="25">
+        <v>0.42</v>
+      </c>
+      <c r="E565" s="26">
+        <v>1.7</v>
+      </c>
+      <c r="F565" s="26">
+        <v>1.63</v>
+      </c>
+      <c r="L565" t="s">
+        <v>103</v>
+      </c>
+      <c r="M565" s="71" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="566" spans="1:13">
+      <c r="A566" s="61">
+        <v>45590</v>
+      </c>
+      <c r="B566" t="s">
+        <v>17</v>
+      </c>
+      <c r="C566" s="35">
+        <v>0</v>
+      </c>
+      <c r="D566" s="25">
+        <v>0.01</v>
+      </c>
+      <c r="E566" s="26">
+        <v>1.4</v>
+      </c>
+      <c r="F566" s="26">
+        <v>1.76</v>
+      </c>
+      <c r="H566" s="35">
+        <v>113</v>
+      </c>
+      <c r="I566" s="25">
+        <v>0.27</v>
+      </c>
+      <c r="J566" s="30">
+        <v>9.5999999999999992E-3</v>
+      </c>
+      <c r="L566" t="s">
+        <v>103</v>
+      </c>
+      <c r="M566" s="71" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="567" spans="1:13">
+      <c r="A567" s="61">
+        <v>45590</v>
+      </c>
+      <c r="B567" t="s">
+        <v>18</v>
+      </c>
+      <c r="C567" s="35">
+        <v>0</v>
+      </c>
+      <c r="D567" s="25">
+        <v>0.04</v>
+      </c>
+      <c r="E567" s="26">
+        <v>1.2</v>
+      </c>
+      <c r="F567" s="26">
+        <v>1.36</v>
+      </c>
+      <c r="H567" s="35">
+        <v>83</v>
+      </c>
+      <c r="I567" s="25">
+        <v>0.19</v>
+      </c>
+      <c r="J567" s="30">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="L567" t="s">
+        <v>103</v>
+      </c>
+      <c r="M567" s="71" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="568" spans="1:13">
+      <c r="A568" s="61">
+        <v>45593</v>
+      </c>
+      <c r="B568" t="s">
+        <v>17</v>
+      </c>
+      <c r="C568" s="35">
+        <v>0</v>
+      </c>
+      <c r="D568" s="25">
+        <v>0.02</v>
+      </c>
+      <c r="E568" s="26">
+        <v>1.3</v>
+      </c>
+      <c r="F568" s="26">
+        <v>1.96</v>
+      </c>
+      <c r="H568" s="35">
+        <v>178</v>
+      </c>
+      <c r="K568" s="25">
+        <v>0</v>
+      </c>
+      <c r="L568" t="s">
+        <v>140</v>
+      </c>
+      <c r="M568" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="569" spans="1:13">
+      <c r="A569" s="61">
+        <v>45593</v>
+      </c>
+      <c r="B569" t="s">
+        <v>18</v>
+      </c>
+      <c r="C569" s="35">
+        <v>0</v>
+      </c>
+      <c r="D569" s="25">
+        <v>1.6E-2</v>
+      </c>
+      <c r="E569" s="26">
+        <v>1.53</v>
+      </c>
+      <c r="F569" s="26">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="H569" s="35">
+        <v>125</v>
+      </c>
+      <c r="K569" s="25">
+        <v>0</v>
+      </c>
+      <c r="L569" t="s">
+        <v>140</v>
+      </c>
+      <c r="M569" s="16" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="570" spans="1:13">
+      <c r="A570" s="72">
+        <v>45597</v>
+      </c>
+      <c r="B570" s="73" t="s">
+        <v>13</v>
+      </c>
+      <c r="C570" s="73">
+        <v>0</v>
+      </c>
+      <c r="D570" s="73">
+        <v>0.01</v>
+      </c>
+      <c r="E570" s="73">
+        <v>1.2</v>
+      </c>
+      <c r="F570" s="73">
+        <v>1.5</v>
+      </c>
+      <c r="G570" s="73">
+        <v>8.19</v>
+      </c>
+      <c r="H570" s="73">
+        <v>130</v>
+      </c>
+      <c r="I570" s="73">
+        <v>0.997</v>
+      </c>
+      <c r="J570" s="73">
+        <v>4.7E-2</v>
+      </c>
+      <c r="K570" s="73"/>
+      <c r="L570" s="73" t="s">
+        <v>99</v>
+      </c>
+      <c r="M570" s="73"/>
+    </row>
+    <row r="571" spans="1:13">
+      <c r="A571" s="72">
+        <v>45597</v>
+      </c>
+      <c r="B571" s="73" t="s">
+        <v>159</v>
+      </c>
+      <c r="C571" s="73">
+        <v>15</v>
+      </c>
+      <c r="D571" s="73">
+        <v>0.33</v>
+      </c>
+      <c r="E571" s="73">
+        <v>1.8</v>
+      </c>
+      <c r="F571" s="73">
+        <v>1.7</v>
+      </c>
+      <c r="G571" s="73"/>
+      <c r="H571" s="73"/>
+      <c r="I571" s="73"/>
+      <c r="J571" s="73"/>
+      <c r="K571" s="73"/>
+      <c r="L571" s="73" t="s">
+        <v>99</v>
+      </c>
+      <c r="M571" s="73"/>
+    </row>
+    <row r="572" spans="1:13">
+      <c r="A572" s="72">
+        <v>45597</v>
+      </c>
+      <c r="B572" s="73" t="s">
+        <v>17</v>
+      </c>
+      <c r="C572" s="73">
+        <v>0</v>
+      </c>
+      <c r="D572" s="73">
+        <v>0.01</v>
+      </c>
+      <c r="E572" s="73">
+        <v>1</v>
+      </c>
+      <c r="F572" s="73">
+        <v>1</v>
+      </c>
+      <c r="G572" s="73">
+        <v>7.99</v>
+      </c>
+      <c r="H572" s="73">
+        <v>105</v>
+      </c>
+      <c r="I572" s="73">
+        <v>0.23</v>
+      </c>
+      <c r="J572" s="73">
+        <v>2.4E-2</v>
+      </c>
+      <c r="K572" s="73"/>
+      <c r="L572" s="73" t="s">
+        <v>99</v>
+      </c>
+      <c r="M572" s="73"/>
+    </row>
+    <row r="573" spans="1:13">
+      <c r="A573" s="72">
+        <v>45597</v>
+      </c>
+      <c r="B573" s="73" t="s">
+        <v>18</v>
+      </c>
+      <c r="C573" s="73">
+        <v>0</v>
+      </c>
+      <c r="D573" s="73">
+        <v>0.05</v>
+      </c>
+      <c r="E573" s="73">
+        <v>1</v>
+      </c>
+      <c r="F573" s="73">
+        <v>1.5</v>
+      </c>
+      <c r="G573" s="73">
+        <v>8.09</v>
+      </c>
+      <c r="H573" s="73">
+        <v>110</v>
+      </c>
+      <c r="I573" s="73">
+        <v>0.373</v>
+      </c>
+      <c r="J573" s="73">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="K573" s="73"/>
+      <c r="L573" s="73" t="s">
+        <v>99</v>
+      </c>
+      <c r="M573" s="73"/>
+    </row>
+    <row r="574" spans="1:13">
+      <c r="A574" s="72">
+        <v>45600</v>
+      </c>
+      <c r="B574" s="73" t="s">
+        <v>17</v>
+      </c>
+      <c r="C574" s="73">
+        <v>0</v>
+      </c>
+      <c r="D574" s="73">
+        <v>0.02</v>
+      </c>
+      <c r="E574" s="73">
+        <v>1.2</v>
+      </c>
+      <c r="F574" s="73">
+        <v>1.53</v>
+      </c>
+      <c r="G574" s="73"/>
+      <c r="H574" s="73">
+        <v>136</v>
+      </c>
+      <c r="I574" s="73"/>
+      <c r="J574" s="73"/>
+      <c r="K574" s="73">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="L574" s="73" t="s">
+        <v>140</v>
+      </c>
+      <c r="M574" s="74" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="575" spans="1:13">
+      <c r="A575" s="72">
+        <v>45600</v>
+      </c>
+      <c r="B575" s="73" t="s">
+        <v>18</v>
+      </c>
+      <c r="C575" s="73">
+        <v>0</v>
+      </c>
+      <c r="D575" s="73">
+        <v>0.03</v>
+      </c>
+      <c r="E575" s="73">
+        <v>1.2</v>
+      </c>
+      <c r="F575" s="73">
+        <v>1.73</v>
+      </c>
+      <c r="G575" s="73"/>
+      <c r="H575" s="73">
+        <v>142</v>
+      </c>
+      <c r="I575" s="73"/>
+      <c r="J575" s="73"/>
+      <c r="K575" s="73">
+        <v>0.02</v>
+      </c>
+      <c r="L575" s="73" t="s">
+        <v>140</v>
+      </c>
+      <c r="M575" s="74" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="576" spans="1:13">
+      <c r="A576" s="61">
+        <v>45604</v>
+      </c>
+      <c r="B576" t="s">
+        <v>13</v>
+      </c>
+      <c r="C576" s="35">
+        <v>0</v>
+      </c>
+      <c r="D576" s="25">
+        <v>0.09</v>
+      </c>
+      <c r="E576" s="26">
+        <v>0.9</v>
+      </c>
+      <c r="F576" s="26">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="G576" s="25">
+        <v>8.18</v>
+      </c>
+      <c r="H576" s="35">
+        <v>133</v>
+      </c>
+      <c r="I576" s="25">
+        <v>1.137</v>
+      </c>
+      <c r="J576" s="30">
+        <v>1.2E-2</v>
+      </c>
+      <c r="L576" t="s">
+        <v>99</v>
+      </c>
+      <c r="M576" s="74"/>
+    </row>
+    <row r="577" spans="1:13">
+      <c r="A577" s="61">
+        <v>45604</v>
+      </c>
+      <c r="B577" t="s">
+        <v>16</v>
+      </c>
+      <c r="C577" s="35">
+        <v>14</v>
+      </c>
+      <c r="D577" s="25">
+        <v>0.35</v>
+      </c>
+      <c r="E577" s="26">
+        <v>1</v>
+      </c>
+      <c r="F577" s="26">
+        <v>0.7</v>
+      </c>
+      <c r="L577" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="578" spans="1:13">
+      <c r="A578" s="61">
+        <v>45604</v>
+      </c>
+      <c r="B578" t="s">
+        <v>17</v>
+      </c>
+      <c r="C578" s="35">
+        <v>0</v>
+      </c>
+      <c r="D578" s="25">
+        <v>0.01</v>
+      </c>
+      <c r="E578" s="26">
+        <v>0.9</v>
+      </c>
+      <c r="F578" s="26">
+        <v>1.4</v>
+      </c>
+      <c r="G578" s="25">
+        <v>8.16</v>
+      </c>
+      <c r="H578" s="35">
+        <v>98</v>
+      </c>
+      <c r="I578" s="25">
+        <v>0.317</v>
+      </c>
+      <c r="J578" s="30">
+        <v>7.5999999999999998E-2</v>
+      </c>
+      <c r="L578" t="s">
+        <v>99</v>
+      </c>
+      <c r="M578" s="73"/>
+    </row>
+    <row r="579" spans="1:13">
+      <c r="A579" s="61">
+        <v>45604</v>
+      </c>
+      <c r="B579" t="s">
+        <v>18</v>
+      </c>
+      <c r="C579" s="35">
+        <v>0</v>
+      </c>
+      <c r="D579" s="25">
+        <v>0.04</v>
+      </c>
+      <c r="E579" s="26">
+        <v>0.9</v>
+      </c>
+      <c r="F579" s="26">
+        <v>1.6</v>
+      </c>
+      <c r="G579" s="25">
+        <v>8.23</v>
+      </c>
+      <c r="H579" s="35">
+        <v>115</v>
+      </c>
+      <c r="I579" s="25">
+        <v>0.37</v>
+      </c>
+      <c r="J579" s="30">
+        <v>0.04</v>
+      </c>
+      <c r="L579" t="s">
+        <v>99</v>
+      </c>
+      <c r="M579" s="73"/>
+    </row>
+    <row r="580" spans="1:13">
+      <c r="A580" s="61">
+        <v>45611</v>
+      </c>
+      <c r="B580" t="s">
+        <v>13</v>
+      </c>
+      <c r="C580" s="35">
+        <v>0</v>
+      </c>
+      <c r="D580" s="25">
+        <v>0.05</v>
+      </c>
+      <c r="E580" s="26">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F580" s="26">
+        <v>1.3</v>
+      </c>
+      <c r="H580" s="35">
+        <v>130</v>
+      </c>
+      <c r="I580" s="25">
+        <v>1.24</v>
+      </c>
+      <c r="J580" s="30">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="L580" t="s">
+        <v>103</v>
+      </c>
+      <c r="M580" s="73" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="581" spans="1:13">
+      <c r="A581" s="61">
+        <v>45611</v>
+      </c>
+      <c r="B581" t="s">
+        <v>16</v>
+      </c>
+      <c r="C581" s="35">
+        <v>14</v>
+      </c>
+      <c r="D581" s="25">
+        <v>0.39</v>
+      </c>
+      <c r="E581" s="26">
+        <v>1.9</v>
+      </c>
+      <c r="F581" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="L581" t="s">
+        <v>103</v>
+      </c>
+      <c r="M581" s="75" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="582" spans="1:13">
+      <c r="A582" s="61">
+        <v>45611</v>
+      </c>
+      <c r="B582" t="s">
+        <v>17</v>
+      </c>
+      <c r="C582" s="35">
+        <v>0</v>
+      </c>
+      <c r="D582" s="25">
+        <v>0.01</v>
+      </c>
+      <c r="E582" s="26">
+        <v>0.9</v>
+      </c>
+      <c r="F582" s="26">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H582" s="35">
+        <v>87</v>
+      </c>
+      <c r="I582" s="25">
+        <v>0.24</v>
+      </c>
+      <c r="J582" s="30">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="L582" t="s">
+        <v>103</v>
+      </c>
+      <c r="M582" s="75" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="583" spans="1:13">
+      <c r="A583" s="61">
+        <v>45611</v>
+      </c>
+      <c r="B583" t="s">
+        <v>18</v>
+      </c>
+      <c r="C583" s="35">
+        <v>0</v>
+      </c>
+      <c r="D583" s="25">
+        <v>0.02</v>
+      </c>
+      <c r="E583" s="26">
+        <v>1.6</v>
+      </c>
+      <c r="F583" s="26">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="H583" s="35">
+        <v>91</v>
+      </c>
+      <c r="I583" s="25">
+        <v>0.52</v>
+      </c>
+      <c r="J583" s="30">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="L583" t="s">
+        <v>103</v>
+      </c>
+      <c r="M583" s="75" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="584" spans="1:13">
+      <c r="A584" s="61">
+        <v>45614</v>
+      </c>
+      <c r="B584" t="s">
+        <v>17</v>
+      </c>
+      <c r="C584" s="35">
+        <v>0</v>
+      </c>
+      <c r="D584" s="25">
+        <v>0.04</v>
+      </c>
+      <c r="E584" s="26">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F584" s="26">
+        <v>1.4</v>
+      </c>
+      <c r="H584" s="35">
+        <v>90</v>
+      </c>
+      <c r="K584" s="25">
+        <v>0</v>
+      </c>
+      <c r="L584" t="s">
+        <v>147</v>
+      </c>
+      <c r="M584" s="75" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="585" spans="1:13">
+      <c r="A585" s="61">
+        <v>45614</v>
+      </c>
+      <c r="B585" t="s">
+        <v>18</v>
+      </c>
+      <c r="C585" s="35">
+        <v>0</v>
+      </c>
+      <c r="D585" s="25">
+        <v>0.43</v>
+      </c>
+      <c r="E585" s="26">
+        <v>1.2</v>
+      </c>
+      <c r="F585" s="26">
+        <v>1.3</v>
+      </c>
+      <c r="H585" s="35">
+        <v>91</v>
+      </c>
+      <c r="K585" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L585" t="s">
+        <v>147</v>
+      </c>
+      <c r="M585" s="75" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="586" spans="1:13">
+      <c r="A586" s="61">
+        <v>45618</v>
+      </c>
+      <c r="B586" t="s">
+        <v>13</v>
+      </c>
+      <c r="C586" s="35">
+        <v>0</v>
+      </c>
+      <c r="D586" s="25">
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="E586" s="26">
+        <v>1.4</v>
+      </c>
+      <c r="F586" s="26">
+        <v>2.27</v>
+      </c>
+      <c r="H586" s="35">
+        <v>129</v>
+      </c>
+      <c r="I586" s="25">
+        <v>1.5</v>
+      </c>
+      <c r="J586" s="30">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="L586" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="587" spans="1:13">
+      <c r="A587" s="61">
+        <v>45618</v>
+      </c>
+      <c r="B587" t="s">
+        <v>16</v>
+      </c>
+      <c r="C587" s="35">
+        <v>17</v>
+      </c>
+      <c r="D587" s="25">
+        <v>0.27700000000000002</v>
+      </c>
+      <c r="E587" s="26">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F587" s="26">
+        <v>1.77</v>
+      </c>
+      <c r="L587" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="588" spans="1:13">
+      <c r="A588" s="61">
+        <v>45618</v>
+      </c>
+      <c r="B588" t="s">
+        <v>17</v>
+      </c>
+      <c r="C588" s="35">
+        <v>0</v>
+      </c>
+      <c r="D588" s="25">
+        <v>0</v>
+      </c>
+      <c r="E588" s="26">
+        <v>1.2</v>
+      </c>
+      <c r="F588" s="26">
+        <v>1.9</v>
+      </c>
+      <c r="H588" s="35">
+        <v>88</v>
+      </c>
+      <c r="I588" s="25">
+        <v>0.25</v>
+      </c>
+      <c r="J588" s="30">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="L588" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="589" spans="1:13">
+      <c r="A589" s="61">
+        <v>45618</v>
+      </c>
+      <c r="B589" t="s">
+        <v>18</v>
+      </c>
+      <c r="C589" s="35">
+        <v>0</v>
+      </c>
+      <c r="D589" s="25">
+        <v>2.3E-2</v>
+      </c>
+      <c r="E589" s="26">
+        <v>1.3</v>
+      </c>
+      <c r="F589" s="26">
+        <v>2</v>
+      </c>
+      <c r="H589" s="35">
+        <v>86</v>
+      </c>
+      <c r="I589" s="25">
+        <v>0.62</v>
+      </c>
+      <c r="J589" s="30">
+        <v>3.9E-2</v>
+      </c>
+    </row>
+    <row r="590" spans="1:13">
+      <c r="A590" s="61">
+        <v>45623</v>
+      </c>
+      <c r="B590" t="s">
+        <v>13</v>
+      </c>
+      <c r="C590" s="35">
+        <v>0</v>
+      </c>
+      <c r="D590" s="25">
+        <v>0.1</v>
+      </c>
+      <c r="E590" s="26">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F590" s="26">
+        <v>1.8</v>
+      </c>
+      <c r="G590" s="25">
+        <v>8.1300000000000008</v>
+      </c>
+      <c r="H590" s="35">
+        <v>125</v>
+      </c>
+      <c r="I590" s="25">
+        <v>1.46</v>
+      </c>
+      <c r="J590" s="30">
+        <v>7.0999999999999994E-2</v>
+      </c>
+      <c r="L590" t="s">
+        <v>27</v>
+      </c>
+      <c r="M590" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="591" spans="1:13">
+      <c r="A591" s="61">
+        <v>45623</v>
+      </c>
+      <c r="B591" t="s">
+        <v>16</v>
+      </c>
+      <c r="C591" s="35">
+        <v>14</v>
+      </c>
+      <c r="D591" s="25">
+        <v>0.43</v>
+      </c>
+      <c r="E591" s="26">
+        <v>1.7</v>
+      </c>
+      <c r="F591" s="26">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="L591" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="592" spans="1:13">
+      <c r="A592" s="61">
+        <v>45623</v>
+      </c>
+      <c r="B592" t="s">
+        <v>17</v>
+      </c>
+      <c r="C592" s="35">
+        <v>0</v>
+      </c>
+      <c r="D592" s="25">
+        <v>0.04</v>
+      </c>
+      <c r="E592" s="26">
+        <v>1.3</v>
+      </c>
+      <c r="F592" s="26">
+        <v>2.1</v>
+      </c>
+      <c r="G592" s="25">
+        <v>8</v>
+      </c>
+      <c r="H592" s="35">
+        <v>83</v>
+      </c>
+      <c r="I592" s="25">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J592" s="30">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="L592" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="593" spans="1:13">
+      <c r="A593" s="61">
+        <v>45623</v>
+      </c>
+      <c r="B593" t="s">
+        <v>18</v>
+      </c>
+      <c r="C593" s="35">
+        <v>0</v>
+      </c>
+      <c r="D593" s="25">
+        <v>0.02</v>
+      </c>
+      <c r="E593" s="26">
+        <v>1.5</v>
+      </c>
+      <c r="F593" s="26">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="G593" s="25">
+        <v>8</v>
+      </c>
+      <c r="H593" s="35">
+        <v>82</v>
+      </c>
+      <c r="I593" s="25">
+        <v>0.83</v>
+      </c>
+      <c r="J593" s="30">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="L593" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="594" spans="1:13">
+      <c r="A594" s="61">
+        <v>45628</v>
+      </c>
+      <c r="B594" t="s">
+        <v>17</v>
+      </c>
+      <c r="C594" s="35">
+        <v>0</v>
+      </c>
+      <c r="D594" s="25">
+        <v>7.2999999999999995E-2</v>
+      </c>
+      <c r="E594" s="26">
+        <v>1.8</v>
+      </c>
+      <c r="F594" s="26">
+        <v>4.13</v>
+      </c>
+      <c r="H594" s="35">
+        <v>46</v>
+      </c>
+      <c r="K594" s="25">
+        <v>0</v>
+      </c>
+      <c r="L594" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="595" spans="1:13">
+      <c r="A595" s="61">
+        <v>45628</v>
+      </c>
+      <c r="B595" t="s">
+        <v>18</v>
+      </c>
+      <c r="C595" s="35">
+        <v>0</v>
+      </c>
+      <c r="D595" s="25">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="E595" s="26">
+        <v>1.3</v>
+      </c>
+      <c r="F595" s="26">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="H595" s="35">
+        <v>115</v>
+      </c>
+      <c r="K595" s="25">
+        <v>0</v>
+      </c>
+      <c r="L595" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="596" spans="1:13">
+      <c r="A596" s="61">
+        <v>45632</v>
+      </c>
+      <c r="B596" t="s">
+        <v>13</v>
+      </c>
+      <c r="C596" s="35">
+        <v>0</v>
+      </c>
+      <c r="D596" s="25">
+        <v>0.06</v>
+      </c>
+      <c r="E596" s="26">
+        <v>0.93</v>
+      </c>
+      <c r="F596" s="26">
+        <v>1.8</v>
+      </c>
+      <c r="G596" s="25">
+        <v>8.07</v>
+      </c>
+      <c r="H596" s="35">
+        <v>121</v>
+      </c>
+      <c r="I596" s="25">
+        <v>1.6659999999999999</v>
+      </c>
+      <c r="J596" s="30">
+        <v>1.2699999999999999E-2</v>
+      </c>
+      <c r="L596" t="s">
+        <v>103</v>
+      </c>
+      <c r="M596" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="597" spans="1:13">
+      <c r="A597" s="61">
+        <v>45632</v>
+      </c>
+      <c r="B597" t="s">
+        <v>16</v>
+      </c>
+      <c r="C597" s="35">
+        <v>14</v>
+      </c>
+      <c r="D597" s="25">
+        <v>0.23</v>
+      </c>
+      <c r="E597" s="26">
+        <v>1.5</v>
+      </c>
+      <c r="F597" s="26">
+        <v>1.6</v>
+      </c>
+      <c r="L597" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="598" spans="1:13">
+      <c r="A598" s="61">
+        <v>45632</v>
+      </c>
+      <c r="B598" t="s">
+        <v>17</v>
+      </c>
+      <c r="C598" s="35">
+        <v>0</v>
+      </c>
+      <c r="D598" s="25">
+        <v>0.02</v>
+      </c>
+      <c r="E598" s="26">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F598" s="26">
+        <v>1.4</v>
+      </c>
+      <c r="G598" s="25">
+        <v>8</v>
+      </c>
+      <c r="H598" s="35">
+        <v>70</v>
+      </c>
+      <c r="I598" s="25">
+        <v>0.55300000000000005</v>
+      </c>
+      <c r="J598" s="30">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="L598" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="599" spans="1:13">
+      <c r="A599" s="61">
+        <v>45632</v>
+      </c>
+      <c r="B599" t="s">
+        <v>18</v>
+      </c>
+      <c r="C599" s="35">
+        <v>0</v>
+      </c>
+      <c r="D599" s="25">
+        <v>0.02</v>
+      </c>
+      <c r="E599" s="26">
+        <v>1</v>
+      </c>
+      <c r="F599" s="26">
+        <v>1.8</v>
+      </c>
+      <c r="G599" s="25">
+        <v>8.0399999999999991</v>
+      </c>
+      <c r="H599" s="35">
+        <v>75</v>
+      </c>
+      <c r="I599" s="25">
+        <v>1.41</v>
+      </c>
+      <c r="J599" s="30">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="L599" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="600" spans="1:13">
+      <c r="A600" s="61">
+        <v>45639</v>
+      </c>
+      <c r="B600" t="s">
+        <v>13</v>
+      </c>
+      <c r="C600" s="35">
+        <v>0</v>
+      </c>
+      <c r="D600" s="25">
+        <v>0.06</v>
+      </c>
+      <c r="E600" s="26">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F600" s="26">
+        <v>1.5</v>
+      </c>
+      <c r="G600" s="25">
+        <v>8.0299999999999994</v>
+      </c>
+      <c r="H600" s="35">
+        <v>125</v>
+      </c>
+      <c r="I600" s="25">
+        <v>1.72</v>
+      </c>
+      <c r="J600" s="30">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="L600" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="601" spans="1:13">
+      <c r="A601" s="61">
+        <v>45639</v>
+      </c>
+      <c r="B601" t="s">
+        <v>16</v>
+      </c>
+      <c r="C601" s="35">
+        <v>14</v>
+      </c>
+      <c r="D601" s="25">
+        <v>0.31</v>
+      </c>
+      <c r="E601" s="26">
+        <v>1.3</v>
+      </c>
+      <c r="F601" s="26">
+        <v>1.3</v>
+      </c>
+      <c r="L601" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="602" spans="1:13">
+      <c r="A602" s="61">
+        <v>45639</v>
+      </c>
+      <c r="B602" t="s">
+        <v>17</v>
+      </c>
+      <c r="C602" s="35">
+        <v>0</v>
+      </c>
+      <c r="D602" s="25">
+        <v>0.05</v>
+      </c>
+      <c r="E602" s="26">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F602" s="26">
+        <v>1.8</v>
+      </c>
+      <c r="G602" s="25">
+        <v>7.95</v>
+      </c>
+      <c r="H602" s="35">
+        <v>83</v>
+      </c>
+      <c r="I602" s="25">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="J602" s="30">
+        <v>4.7E-2</v>
+      </c>
+      <c r="L602" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="603" spans="1:13">
+      <c r="A603" s="61">
+        <v>45639</v>
+      </c>
+      <c r="B603" t="s">
+        <v>18</v>
+      </c>
+      <c r="C603" s="35">
+        <v>0</v>
+      </c>
+      <c r="D603" s="25">
+        <v>0.02</v>
+      </c>
+      <c r="E603" s="26">
+        <v>1.5</v>
+      </c>
+      <c r="F603" s="26">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="G603" s="25">
+        <v>7.98</v>
+      </c>
+      <c r="H603" s="35">
+        <v>110</v>
+      </c>
+      <c r="I603" s="25">
+        <v>1.72</v>
+      </c>
+      <c r="J603" s="30">
+        <v>0.04</v>
+      </c>
+      <c r="L603" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="604" spans="1:13">
+      <c r="A604" s="61">
+        <v>45653</v>
+      </c>
+      <c r="B604" t="s">
+        <v>13</v>
+      </c>
+      <c r="C604" s="35">
+        <v>0</v>
+      </c>
+      <c r="D604" s="25">
+        <v>0.05</v>
+      </c>
+      <c r="E604" s="26">
+        <v>1</v>
+      </c>
+      <c r="F604" s="26">
+        <v>1.6</v>
+      </c>
+      <c r="G604" s="25">
+        <v>7.97</v>
+      </c>
+      <c r="H604" s="35">
+        <v>122</v>
+      </c>
+      <c r="I604" s="25">
+        <v>1.69</v>
+      </c>
+      <c r="J604" s="30">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="L604" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="605" spans="1:13">
+      <c r="A605" s="61">
+        <v>45653</v>
+      </c>
+      <c r="B605" t="s">
+        <v>16</v>
+      </c>
+      <c r="C605" s="35">
+        <v>10</v>
+      </c>
+      <c r="D605" s="25">
+        <v>0.34</v>
+      </c>
+      <c r="E605" s="26">
+        <v>1</v>
+      </c>
+      <c r="F605" s="26">
+        <v>1.2</v>
+      </c>
+      <c r="L605" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="606" spans="1:13">
+      <c r="A606" s="61">
+        <v>45653</v>
+      </c>
+      <c r="B606" t="s">
+        <v>17</v>
+      </c>
+      <c r="C606" s="35">
+        <v>0</v>
+      </c>
+      <c r="D606" s="25">
+        <v>0</v>
+      </c>
+      <c r="E606" s="26">
+        <v>1.3</v>
+      </c>
+      <c r="F606" s="26">
+        <v>1.9</v>
+      </c>
+      <c r="G606" s="25">
+        <v>8.01</v>
+      </c>
+      <c r="H606" s="35">
+        <v>67</v>
+      </c>
+      <c r="I606" s="25">
+        <v>0.23</v>
+      </c>
+      <c r="J606" s="30">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="L606" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="607" spans="1:13">
+      <c r="A607" s="61">
+        <v>45653</v>
+      </c>
+      <c r="B607" t="s">
+        <v>18</v>
+      </c>
+      <c r="C607" s="35">
+        <v>0</v>
+      </c>
+      <c r="D607" s="25">
+        <v>0.03</v>
+      </c>
+      <c r="E607" s="26">
+        <v>1.5</v>
+      </c>
+      <c r="F607" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="G607" s="25">
+        <v>8.0500000000000007</v>
+      </c>
+      <c r="H607" s="35">
+        <v>74</v>
+      </c>
+      <c r="I607" s="25">
+        <v>1.34</v>
+      </c>
+      <c r="J607" s="30">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="L607" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="608" spans="1:13">
+      <c r="A608" s="61">
+        <v>45667</v>
+      </c>
+      <c r="B608" t="s">
+        <v>13</v>
+      </c>
+      <c r="C608" s="35">
+        <v>0</v>
+      </c>
+      <c r="D608" s="25">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="E608" s="26">
+        <v>0.9</v>
+      </c>
+      <c r="F608" s="26">
+        <v>1.7</v>
+      </c>
+      <c r="G608" s="25">
+        <v>7.78</v>
+      </c>
+      <c r="H608" s="35">
+        <v>124</v>
+      </c>
+      <c r="I608" s="25">
+        <v>1.9</v>
+      </c>
+      <c r="J608" s="30">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="L608" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="609" spans="1:13">
+      <c r="A609" s="61">
+        <v>45667</v>
+      </c>
+      <c r="B609" t="s">
+        <v>16</v>
+      </c>
+      <c r="C609" s="35">
+        <v>13</v>
+      </c>
+      <c r="D609" s="25">
+        <v>0.36</v>
+      </c>
+      <c r="E609" s="26">
+        <v>1.2</v>
+      </c>
+      <c r="F609" s="26">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="L609" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="610" spans="1:13">
+      <c r="A610" s="61">
+        <v>45667</v>
+      </c>
+      <c r="B610" t="s">
+        <v>17</v>
+      </c>
+      <c r="C610" s="35">
+        <v>0</v>
+      </c>
+      <c r="D610" s="25">
+        <v>0.01</v>
+      </c>
+      <c r="E610" s="26">
+        <v>0.8</v>
+      </c>
+      <c r="F610" s="26">
+        <v>1.3</v>
+      </c>
+      <c r="G610" s="25">
+        <v>7.89</v>
+      </c>
+      <c r="H610" s="35">
+        <v>77</v>
+      </c>
+      <c r="I610" s="25">
+        <v>0.25</v>
+      </c>
+      <c r="J610" s="30">
+        <v>0.04</v>
+      </c>
+      <c r="L610" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="611" spans="1:13">
+      <c r="A611" s="61">
+        <v>45667</v>
+      </c>
+      <c r="B611" t="s">
+        <v>18</v>
+      </c>
+      <c r="C611" s="35">
+        <v>0</v>
+      </c>
+      <c r="D611" s="25">
+        <v>0.04</v>
+      </c>
+      <c r="E611" s="26">
+        <v>1.3</v>
+      </c>
+      <c r="F611" s="26">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="G611" s="25">
+        <v>8</v>
+      </c>
+      <c r="H611" s="35">
+        <v>106</v>
+      </c>
+      <c r="I611" s="25">
+        <v>0.42</v>
+      </c>
+      <c r="J611" s="30">
+        <v>0.04</v>
+      </c>
+      <c r="L611" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="612" spans="1:13">
+      <c r="A612" s="61">
+        <v>45670</v>
+      </c>
+      <c r="B612" t="s">
+        <v>17</v>
+      </c>
+      <c r="C612" s="35">
+        <v>0</v>
+      </c>
+      <c r="D612" s="25">
+        <v>0.03</v>
+      </c>
+      <c r="E612" s="26">
+        <v>1</v>
+      </c>
+      <c r="F612" s="26">
+        <v>1.67</v>
+      </c>
+      <c r="H612" s="35">
+        <v>86</v>
+      </c>
+      <c r="K612" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L612" t="s">
+        <v>34</v>
+      </c>
+      <c r="M612" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="613" spans="1:13">
+      <c r="A613" s="61">
+        <v>45670</v>
+      </c>
+      <c r="B613" t="s">
+        <v>18</v>
+      </c>
+      <c r="C613" s="35">
+        <v>0</v>
+      </c>
+      <c r="D613" s="25">
+        <v>0.03</v>
+      </c>
+      <c r="E613" s="26">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F613" s="26">
+        <v>1.7</v>
+      </c>
+      <c r="H613" s="35">
+        <v>85</v>
+      </c>
+      <c r="K613" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L613" t="s">
+        <v>34</v>
+      </c>
+      <c r="M613" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="614" spans="1:13">
+      <c r="A614" s="61">
+        <v>45674</v>
+      </c>
+      <c r="B614" t="s">
+        <v>13</v>
+      </c>
+      <c r="C614" s="35">
+        <v>0</v>
+      </c>
+      <c r="D614" s="25">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="E614" s="26">
+        <v>0.93</v>
+      </c>
+      <c r="F614" s="26">
+        <v>1.4</v>
+      </c>
+      <c r="G614" s="25">
+        <v>7.88</v>
+      </c>
+      <c r="H614" s="35">
+        <v>124</v>
+      </c>
+      <c r="I614" s="25">
+        <v>1.96</v>
+      </c>
+      <c r="J614" s="30">
+        <v>4.7E-2</v>
+      </c>
+      <c r="L614" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="615" spans="1:13">
+      <c r="A615" s="61">
+        <v>45674</v>
+      </c>
+      <c r="B615" t="s">
+        <v>16</v>
+      </c>
+      <c r="C615" s="35">
+        <v>16</v>
+      </c>
+      <c r="D615" s="25">
+        <v>0.35599999999999998</v>
+      </c>
+      <c r="E615" s="26">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F615" s="26">
+        <v>1.2</v>
+      </c>
+      <c r="L615" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="616" spans="1:13">
+      <c r="A616" s="61">
+        <v>45674</v>
+      </c>
+      <c r="B616" t="s">
+        <v>17</v>
+      </c>
+      <c r="C616" s="35">
+        <v>0</v>
+      </c>
+      <c r="D616" s="25">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="E616" s="26">
+        <v>0.8</v>
+      </c>
+      <c r="F616" s="26">
+        <v>1.26</v>
+      </c>
+      <c r="G616" s="25">
+        <v>7.86</v>
+      </c>
+      <c r="H616" s="35">
+        <v>78</v>
+      </c>
+      <c r="I616" s="25">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="J616" s="30">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="L616" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="617" spans="1:13">
+      <c r="A617" s="61">
+        <v>45674</v>
+      </c>
+      <c r="B617" t="s">
+        <v>18</v>
+      </c>
+      <c r="C617" s="35">
+        <v>0</v>
+      </c>
+      <c r="D617" s="25">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="E617" s="26">
+        <v>1.4</v>
+      </c>
+      <c r="F617" s="26">
+        <v>1.96</v>
+      </c>
+      <c r="G617" s="25">
+        <v>7.76</v>
+      </c>
+      <c r="H617" s="35">
+        <v>107</v>
+      </c>
+      <c r="I617" s="25">
+        <v>0.36299999999999999</v>
+      </c>
+      <c r="J617" s="30">
+        <v>4.7E-2</v>
+      </c>
+      <c r="L617" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="618" spans="1:13">
+      <c r="A618" s="61">
+        <v>45681</v>
+      </c>
+      <c r="B618" t="s">
+        <v>17</v>
+      </c>
+      <c r="C618" s="35">
+        <v>0</v>
+      </c>
+      <c r="D618" s="25">
+        <v>0</v>
+      </c>
+      <c r="E618" s="26">
+        <v>1.2</v>
+      </c>
+      <c r="F618" s="26">
+        <v>1.7</v>
+      </c>
+      <c r="G618" s="25">
+        <v>7.8</v>
+      </c>
+      <c r="H618" s="35">
+        <v>86</v>
+      </c>
+      <c r="I618" s="25">
+        <v>0.19</v>
+      </c>
+      <c r="J618" s="30">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="L618" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="619" spans="1:13">
+      <c r="A619" s="61">
+        <v>45681</v>
+      </c>
+      <c r="B619" t="s">
+        <v>18</v>
+      </c>
+      <c r="C619" s="35">
+        <v>0</v>
+      </c>
+      <c r="D619" s="25">
+        <v>0.03</v>
+      </c>
+      <c r="E619" s="26">
+        <v>1.6</v>
+      </c>
+      <c r="F619" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="G619" s="25">
+        <v>7.85</v>
+      </c>
+      <c r="H619" s="35">
+        <v>108</v>
+      </c>
+      <c r="I619" s="25">
+        <v>0.72</v>
+      </c>
+      <c r="J619" s="30">
+        <v>0.02</v>
+      </c>
+      <c r="L619" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="620" spans="1:13">
+      <c r="A620" s="61">
+        <v>45681</v>
+      </c>
+      <c r="B620" t="s">
+        <v>13</v>
+      </c>
+      <c r="C620" s="35">
+        <v>0</v>
+      </c>
+      <c r="D620" s="25">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="E620" s="26">
+        <v>0.9</v>
+      </c>
+      <c r="F620" s="26">
+        <v>0.96</v>
+      </c>
+      <c r="G620" s="25">
+        <v>7.88</v>
+      </c>
+      <c r="H620" s="35">
+        <v>132</v>
+      </c>
+      <c r="I620" s="25">
+        <v>1.83</v>
+      </c>
+      <c r="J620" s="30">
+        <v>0.01</v>
+      </c>
+      <c r="L620" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="621" spans="1:13">
+      <c r="A621" s="61">
+        <v>45681</v>
+      </c>
+      <c r="B621" t="s">
+        <v>16</v>
+      </c>
+      <c r="C621" s="35">
+        <v>14</v>
+      </c>
+      <c r="D621" s="25">
+        <v>0.24</v>
+      </c>
+      <c r="E621" s="26">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F621" s="26">
+        <v>1.36</v>
+      </c>
+      <c r="L621" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="622" spans="1:13">
+      <c r="A622" s="61">
+        <v>45681</v>
+      </c>
+      <c r="B622" s="61" t="s">
+        <v>17</v>
+      </c>
+      <c r="C622" s="35">
+        <v>0</v>
+      </c>
+      <c r="D622" s="25">
+        <v>0.01</v>
+      </c>
+      <c r="E622" s="26">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F622" s="26">
+        <v>1.7</v>
+      </c>
+      <c r="H622" s="35">
+        <v>66</v>
+      </c>
+      <c r="K622" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L622" t="s">
+        <v>34</v>
+      </c>
+      <c r="M622" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="623" spans="1:13">
+      <c r="A623" s="61">
+        <v>45684</v>
+      </c>
+      <c r="B623" t="s">
+        <v>18</v>
+      </c>
+      <c r="C623" s="35">
+        <v>0</v>
+      </c>
+      <c r="D623" s="25">
+        <v>0.02</v>
+      </c>
+      <c r="E623" s="26">
+        <v>1.2</v>
+      </c>
+      <c r="F623" s="26">
+        <v>1.9</v>
+      </c>
+      <c r="H623" s="35">
+        <v>94</v>
+      </c>
+      <c r="K623" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L623" t="s">
+        <v>34</v>
+      </c>
+      <c r="M623" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="624" spans="1:13">
+      <c r="A624" s="61">
+        <v>45684</v>
+      </c>
+      <c r="B624" t="s">
+        <v>13</v>
+      </c>
+      <c r="K624" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L624" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="625" spans="1:13">
+      <c r="A625" s="61">
+        <v>45688</v>
+      </c>
+      <c r="B625" t="s">
+        <v>13</v>
+      </c>
+      <c r="C625" s="35">
+        <v>0</v>
+      </c>
+      <c r="D625" s="25">
+        <v>0.02</v>
+      </c>
+      <c r="E625" s="26">
+        <v>0.97</v>
+      </c>
+      <c r="F625" s="26">
+        <v>1.43</v>
+      </c>
+      <c r="G625" s="25">
+        <v>8.16</v>
+      </c>
+      <c r="H625" s="35">
+        <v>123</v>
+      </c>
+      <c r="I625" s="25">
+        <v>1.77</v>
+      </c>
+      <c r="J625" s="30">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="L625" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="626" spans="1:13">
+      <c r="A626" s="61">
+        <v>45688</v>
+      </c>
+      <c r="B626" t="s">
+        <v>16</v>
+      </c>
+      <c r="C626" s="35">
+        <v>14</v>
+      </c>
+      <c r="D626" s="25">
+        <v>0.21</v>
+      </c>
+      <c r="E626" s="26">
+        <v>0.83</v>
+      </c>
+      <c r="F626" s="26">
+        <v>1.2</v>
+      </c>
+      <c r="L626" s="71" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="627" spans="1:13">
+      <c r="A627" s="61">
+        <v>45688</v>
+      </c>
+      <c r="B627" t="s">
+        <v>17</v>
+      </c>
+      <c r="C627" s="35">
+        <v>0</v>
+      </c>
+      <c r="D627" s="25">
+        <v>0.01</v>
+      </c>
+      <c r="E627" s="26">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F627" s="26">
+        <v>1.77</v>
+      </c>
+      <c r="G627" s="25">
+        <v>7.93</v>
+      </c>
+      <c r="H627" s="35">
+        <v>79</v>
+      </c>
+      <c r="I627" s="25">
+        <v>0.19</v>
+      </c>
+      <c r="J627" s="30">
+        <v>0.03</v>
+      </c>
+      <c r="L627" s="71" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="628" spans="1:13">
+      <c r="A628" s="61">
+        <v>45688</v>
+      </c>
+      <c r="B628" t="s">
+        <v>18</v>
+      </c>
+      <c r="C628" s="35">
+        <v>0</v>
+      </c>
+      <c r="D628" s="25">
+        <v>0.02</v>
+      </c>
+      <c r="E628" s="26">
+        <v>1.37</v>
+      </c>
+      <c r="F628" s="26">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="G628" s="25">
+        <v>8.06</v>
+      </c>
+      <c r="H628" s="35">
+        <v>100</v>
+      </c>
+      <c r="I628" s="25">
+        <v>0.92</v>
+      </c>
+      <c r="J628" s="30">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="L628" s="71" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="629" spans="1:13">
+      <c r="A629" s="61">
+        <v>45691</v>
+      </c>
+      <c r="B629" t="s">
+        <v>17</v>
+      </c>
+      <c r="C629" s="35">
+        <v>0</v>
+      </c>
+      <c r="D629" s="25">
+        <v>0</v>
+      </c>
+      <c r="E629" s="26">
+        <v>1.4</v>
+      </c>
+      <c r="F629" s="26">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="H629" s="35">
+        <v>67</v>
+      </c>
+      <c r="K629" s="25">
+        <v>0</v>
+      </c>
+      <c r="L629" t="s">
+        <v>34</v>
+      </c>
+      <c r="M629" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="630" spans="1:13">
+      <c r="A630" s="61">
+        <v>45691</v>
+      </c>
+      <c r="B630" t="s">
+        <v>18</v>
+      </c>
+      <c r="C630" s="35">
+        <v>9</v>
+      </c>
+      <c r="D630" s="25">
+        <v>0.01</v>
+      </c>
+      <c r="E630" s="26">
+        <v>1.2</v>
+      </c>
+      <c r="F630" s="26">
+        <v>1.4</v>
+      </c>
+      <c r="H630" s="35">
+        <v>92</v>
+      </c>
+      <c r="K630" s="25">
+        <v>0.03</v>
+      </c>
+      <c r="L630" t="s">
+        <v>34</v>
+      </c>
+      <c r="M630" s="76" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="631" spans="1:13">
+      <c r="A631" s="61">
+        <v>45695</v>
+      </c>
+      <c r="B631" t="s">
+        <v>13</v>
+      </c>
+      <c r="C631" s="35">
+        <v>0</v>
+      </c>
+      <c r="D631" s="25">
+        <v>0.03</v>
+      </c>
+      <c r="E631" s="26">
+        <v>1.3</v>
+      </c>
+      <c r="F631" s="26">
+        <v>2.1</v>
+      </c>
+      <c r="G631" s="25">
+        <v>7.98</v>
+      </c>
+      <c r="H631" s="35">
+        <v>138</v>
+      </c>
+      <c r="I631" s="25">
+        <v>1.74</v>
+      </c>
+      <c r="J631" s="30">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="L631" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="632" spans="1:13">
+      <c r="A632" s="61">
+        <v>45695</v>
+      </c>
+      <c r="B632" t="s">
+        <v>16</v>
+      </c>
+      <c r="C632" s="35">
+        <v>12</v>
+      </c>
+      <c r="D632" s="25">
+        <v>0.21</v>
+      </c>
+      <c r="E632" s="26">
+        <v>1.3</v>
+      </c>
+      <c r="F632" s="26">
+        <v>1.5</v>
+      </c>
+      <c r="L632" s="76" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="633" spans="1:13">
+      <c r="A633" s="61">
+        <v>45695</v>
+      </c>
+      <c r="B633" t="s">
+        <v>17</v>
+      </c>
+      <c r="C633" s="35">
+        <v>0</v>
+      </c>
+      <c r="D633" s="25">
+        <v>0.04</v>
+      </c>
+      <c r="E633" s="26">
+        <v>1.2</v>
+      </c>
+      <c r="F633" s="26">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="G633" s="25">
+        <v>7.82</v>
+      </c>
+      <c r="H633" s="35">
+        <v>74</v>
+      </c>
+      <c r="I633" s="25">
+        <v>0.18</v>
+      </c>
+      <c r="J633" s="30">
+        <v>7.9000000000000001E-2</v>
+      </c>
+      <c r="L633" s="76" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="634" spans="1:13">
+      <c r="A634" s="61">
+        <v>45695</v>
+      </c>
+      <c r="B634" t="s">
+        <v>18</v>
+      </c>
+      <c r="C634" s="35">
+        <v>0</v>
+      </c>
+      <c r="D634" s="25">
+        <v>0.03</v>
+      </c>
+      <c r="E634" s="26">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F634" s="26">
+        <v>1.8</v>
+      </c>
+      <c r="G634" s="25">
+        <v>8.02</v>
+      </c>
+      <c r="H634" s="35">
+        <v>77</v>
+      </c>
+      <c r="I634" s="25">
+        <v>0.76</v>
+      </c>
+      <c r="J634" s="30">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="L634" s="76" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="635" spans="1:13">
+      <c r="A635" s="61">
+        <v>45698</v>
+      </c>
+      <c r="B635" t="s">
+        <v>17</v>
+      </c>
+      <c r="C635" s="35">
+        <v>0</v>
+      </c>
+      <c r="D635" s="25">
+        <v>0</v>
+      </c>
+      <c r="E635" s="26">
+        <v>1.2</v>
+      </c>
+      <c r="F635" s="26">
+        <v>1.5</v>
+      </c>
+      <c r="H635" s="35">
+        <v>126</v>
+      </c>
+      <c r="K635" s="25">
+        <v>0</v>
+      </c>
+      <c r="L635" t="s">
+        <v>140</v>
+      </c>
+      <c r="M635" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="636" spans="1:13">
+      <c r="A636" s="61">
+        <v>45698</v>
+      </c>
+      <c r="B636" t="s">
+        <v>18</v>
+      </c>
+      <c r="C636" s="35">
+        <v>0</v>
+      </c>
+      <c r="D636" s="25">
+        <v>0.02</v>
+      </c>
+      <c r="E636" s="26">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F636" s="26">
+        <v>1.8</v>
+      </c>
+      <c r="H636" s="35">
+        <v>157</v>
+      </c>
+      <c r="K636" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L636" t="s">
+        <v>140</v>
+      </c>
+      <c r="M636" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="637" spans="1:13">
+      <c r="A637" s="61">
+        <v>45702</v>
+      </c>
+      <c r="B637" t="s">
+        <v>13</v>
+      </c>
+      <c r="C637" s="35">
+        <v>0</v>
+      </c>
+      <c r="D637" s="25">
+        <v>0.19</v>
+      </c>
+      <c r="E637" s="26">
+        <v>1.6</v>
+      </c>
+      <c r="F637" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="G637" s="25">
+        <v>8.16</v>
+      </c>
+      <c r="H637" s="35">
+        <v>123</v>
+      </c>
+      <c r="I637" s="25">
+        <v>1.516</v>
+      </c>
+      <c r="J637" s="30">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="L637" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="638" spans="1:13">
+      <c r="A638" s="70">
+        <v>45702</v>
+      </c>
+      <c r="B638" t="s">
+        <v>16</v>
+      </c>
+      <c r="C638" s="35">
+        <v>12</v>
+      </c>
+      <c r="D638" s="25">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="E638" s="26">
+        <v>1.4</v>
+      </c>
+      <c r="F638" s="26">
+        <v>1.6</v>
+      </c>
+      <c r="L638" s="71" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="639" spans="1:13">
+      <c r="A639" s="70">
+        <v>45702</v>
+      </c>
+      <c r="B639" t="s">
+        <v>17</v>
+      </c>
+      <c r="C639" s="35">
+        <v>0</v>
+      </c>
+      <c r="D639" s="25">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="E639" s="26">
+        <v>1.26</v>
+      </c>
+      <c r="F639" s="26">
+        <v>1.9</v>
+      </c>
+      <c r="G639" s="25">
+        <v>7.69</v>
+      </c>
+      <c r="H639" s="35">
+        <v>73</v>
+      </c>
+      <c r="I639" s="25">
+        <v>0.22</v>
+      </c>
+      <c r="J639" s="30">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="L639" s="71" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="640" spans="1:13">
+      <c r="A640" s="70">
+        <v>45702</v>
+      </c>
+      <c r="B640" t="s">
+        <v>18</v>
+      </c>
+      <c r="C640" s="35">
+        <v>0</v>
+      </c>
+      <c r="D640" s="25">
+        <v>0.03</v>
+      </c>
+      <c r="E640" s="26">
+        <v>2.06</v>
+      </c>
+      <c r="F640" s="26">
+        <v>3.06</v>
+      </c>
+      <c r="G640" s="25">
+        <v>7.67</v>
+      </c>
+      <c r="H640" s="35">
+        <v>109</v>
+      </c>
+      <c r="I640" s="25">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J640" s="30">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="L640" s="71" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="641" spans="1:13">
+      <c r="A641" s="61">
+        <v>45705</v>
+      </c>
+      <c r="B641" t="s">
+        <v>17</v>
+      </c>
+      <c r="C641" s="35">
+        <v>0</v>
+      </c>
+      <c r="D641" s="25">
+        <v>0.05</v>
+      </c>
+      <c r="E641" s="26">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F641" s="26">
+        <v>1.7</v>
+      </c>
+      <c r="H641" s="35">
+        <v>123</v>
+      </c>
+      <c r="K641" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L641" t="s">
+        <v>140</v>
+      </c>
+      <c r="M641" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="642" spans="1:13">
+      <c r="A642" s="61">
+        <v>45705</v>
+      </c>
+      <c r="B642" t="s">
+        <v>18</v>
+      </c>
+      <c r="C642" s="35">
+        <v>0</v>
+      </c>
+      <c r="D642" s="25">
+        <v>0</v>
+      </c>
+      <c r="E642" s="26">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F642" s="26">
+        <v>1.7</v>
+      </c>
+      <c r="H642" s="35">
+        <v>110</v>
+      </c>
+      <c r="K642" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L642" t="s">
+        <v>140</v>
+      </c>
+      <c r="M642" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="643" spans="1:13">
+      <c r="A643" s="61">
+        <v>45709</v>
+      </c>
+      <c r="B643" t="s">
+        <v>13</v>
+      </c>
+      <c r="C643" s="35">
+        <v>0</v>
+      </c>
+      <c r="D643" s="25">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="E643" s="26">
+        <v>1.46</v>
+      </c>
+      <c r="F643" s="26">
+        <v>1.93</v>
+      </c>
+      <c r="G643" s="25">
+        <v>8.25</v>
+      </c>
+      <c r="H643" s="35">
+        <v>126</v>
+      </c>
+      <c r="I643" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="J643" s="30">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="L643" t="s">
+        <v>179</v>
+      </c>
+      <c r="M643" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="644" spans="1:13">
+      <c r="A644" s="61">
+        <v>45709</v>
+      </c>
+      <c r="B644" t="s">
+        <v>16</v>
+      </c>
+      <c r="C644" s="35">
+        <v>13</v>
+      </c>
+      <c r="D644" s="25">
+        <v>0.35599999999999998</v>
+      </c>
+      <c r="E644" s="26">
+        <v>0.9</v>
+      </c>
+      <c r="F644" s="26">
+        <v>0.96599999999999997</v>
+      </c>
+      <c r="L644" s="71" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="645" spans="1:13">
+      <c r="A645" s="61">
+        <v>45709</v>
+      </c>
+      <c r="B645" t="s">
+        <v>17</v>
+      </c>
+      <c r="C645" s="35">
+        <v>0</v>
+      </c>
+      <c r="D645" s="25">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="E645" s="26">
+        <v>1.3</v>
+      </c>
+      <c r="F645" s="26">
+        <v>1.9</v>
+      </c>
+      <c r="G645" s="25">
+        <v>8.01</v>
+      </c>
+      <c r="H645" s="35">
+        <v>107</v>
+      </c>
+      <c r="I645" s="25">
+        <v>0.66</v>
+      </c>
+      <c r="J645" s="30">
+        <v>3.5000000000000001E-3</v>
+      </c>
+      <c r="L645" s="71" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="646" spans="1:13">
+      <c r="A646" s="61">
+        <v>45709</v>
+      </c>
+      <c r="B646" t="s">
+        <v>18</v>
+      </c>
+      <c r="C646" s="35">
+        <v>0</v>
+      </c>
+      <c r="D646" s="25">
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="E646" s="26">
+        <v>1.46</v>
+      </c>
+      <c r="F646" s="26">
+        <v>2.23</v>
+      </c>
+      <c r="G646" s="25">
+        <v>8.0299999999999994</v>
+      </c>
+      <c r="H646" s="35">
+        <v>112</v>
+      </c>
+      <c r="I646" s="25">
+        <v>1.6859999999999999</v>
+      </c>
+      <c r="J646" s="30">
+        <v>0.02</v>
+      </c>
+      <c r="L646" s="71" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="647" spans="1:13">
+      <c r="A647" s="61">
+        <v>45712</v>
+      </c>
+      <c r="B647" t="s">
+        <v>17</v>
+      </c>
+      <c r="C647" s="35">
+        <v>0</v>
+      </c>
+      <c r="D647" s="25">
+        <v>0.01</v>
+      </c>
+      <c r="E647" s="26">
+        <v>1.4</v>
+      </c>
+      <c r="F647" s="26">
+        <v>2</v>
+      </c>
+      <c r="H647" s="35">
+        <v>135</v>
+      </c>
+      <c r="K647" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L647" t="s">
+        <v>140</v>
+      </c>
+      <c r="M647" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="648" spans="1:13">
+      <c r="A648" s="61">
+        <v>45712</v>
+      </c>
+      <c r="B648" t="s">
+        <v>18</v>
+      </c>
+      <c r="C648" s="35">
+        <v>0</v>
+      </c>
+      <c r="D648" s="25">
+        <v>0</v>
+      </c>
+      <c r="E648" s="26">
+        <v>1.3</v>
+      </c>
+      <c r="F648" s="26">
+        <v>1.9</v>
+      </c>
+      <c r="H648" s="35">
+        <v>121</v>
+      </c>
+      <c r="K648" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L648" t="s">
+        <v>140</v>
+      </c>
+      <c r="M648" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="649" spans="1:13">
+      <c r="A649" s="61">
+        <v>45716</v>
+      </c>
+      <c r="B649" t="s">
+        <v>13</v>
+      </c>
+      <c r="C649" s="35">
+        <v>0</v>
+      </c>
+      <c r="D649" s="25">
+        <v>0.06</v>
+      </c>
+      <c r="E649" s="26">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F649" s="26">
+        <v>2</v>
+      </c>
+      <c r="G649" s="25">
+        <v>7.94</v>
+      </c>
+      <c r="H649" s="35">
+        <v>122</v>
+      </c>
+      <c r="I649" s="25">
+        <v>1.667</v>
+      </c>
+      <c r="J649" s="30">
+        <v>0</v>
+      </c>
+      <c r="L649" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="650" spans="1:13">
+      <c r="A650" s="61">
+        <v>45716</v>
+      </c>
+      <c r="B650" t="s">
+        <v>16</v>
+      </c>
+      <c r="C650" s="35">
+        <v>16</v>
+      </c>
+      <c r="D650" s="25">
+        <v>0.22</v>
+      </c>
+      <c r="E650" s="26">
+        <v>1.5</v>
+      </c>
+      <c r="F650" s="26">
+        <v>1.8</v>
+      </c>
+      <c r="K650" s="25">
+        <v>0</v>
+      </c>
+      <c r="L650" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="651" spans="1:13">
+      <c r="A651" s="61">
+        <v>45716</v>
+      </c>
+      <c r="B651" t="s">
+        <v>17</v>
+      </c>
+      <c r="C651" s="35">
+        <v>0</v>
+      </c>
+      <c r="D651" s="25">
+        <v>0.02</v>
+      </c>
+      <c r="E651" s="26">
+        <v>1.4</v>
+      </c>
+      <c r="F651" s="26">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G651" s="25">
+        <v>7.89</v>
+      </c>
+      <c r="H651" s="35">
+        <v>102</v>
+      </c>
+      <c r="I651" s="25">
+        <v>0.223</v>
+      </c>
+      <c r="J651" s="30">
+        <v>2.7E-2</v>
+      </c>
+      <c r="L651" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="652" spans="1:13">
+      <c r="A652" s="61">
+        <v>45716</v>
+      </c>
+      <c r="B652" t="s">
+        <v>18</v>
+      </c>
+      <c r="C652" s="35">
+        <v>0</v>
+      </c>
+      <c r="D652" s="25">
+        <v>0.01</v>
+      </c>
+      <c r="E652" s="26">
+        <v>1.5</v>
+      </c>
+      <c r="F652" s="26">
+        <v>2.1</v>
+      </c>
+      <c r="G652" s="25">
+        <v>7.91</v>
+      </c>
+      <c r="H652" s="35">
+        <v>91</v>
+      </c>
+      <c r="I652" s="25">
+        <v>0.61699999999999999</v>
+      </c>
+      <c r="J652" s="30">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="L652" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="653" spans="1:13">
+      <c r="A653" s="61">
+        <v>45719</v>
+      </c>
+      <c r="B653" t="s">
+        <v>17</v>
+      </c>
+      <c r="C653" s="35">
+        <v>0</v>
+      </c>
+      <c r="D653" s="25">
+        <v>0</v>
+      </c>
+      <c r="E653" s="26">
+        <v>1.36</v>
+      </c>
+      <c r="F653" s="26">
+        <v>1.9</v>
+      </c>
+      <c r="H653" s="35">
+        <v>160</v>
+      </c>
+      <c r="K653" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L653" t="s">
+        <v>140</v>
+      </c>
+      <c r="M653" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="654" spans="1:13">
+      <c r="A654" s="61">
+        <v>45719</v>
+      </c>
+      <c r="B654" t="s">
+        <v>18</v>
+      </c>
+      <c r="C654" s="35">
+        <v>0</v>
+      </c>
+      <c r="D654" s="25">
+        <v>6.3E-2</v>
+      </c>
+      <c r="E654" s="26">
+        <v>1.43</v>
+      </c>
+      <c r="F654" s="26">
+        <v>1.66</v>
+      </c>
+      <c r="H654" s="35">
+        <v>164</v>
+      </c>
+      <c r="K654" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L654" t="s">
+        <v>140</v>
+      </c>
+      <c r="M654" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="655" spans="1:13">
+      <c r="A655" s="61">
+        <v>45719</v>
+      </c>
+      <c r="B655" t="s">
+        <v>13</v>
+      </c>
+      <c r="K655" s="25">
+        <v>0</v>
+      </c>
+      <c r="L655" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="656" spans="1:13">
+      <c r="A656" s="61">
+        <v>45723</v>
+      </c>
+      <c r="B656" t="s">
+        <v>13</v>
+      </c>
+      <c r="C656" s="35">
+        <v>0</v>
+      </c>
+      <c r="D656" s="25">
+        <v>0</v>
+      </c>
+      <c r="E656" s="26">
+        <v>0.96</v>
+      </c>
+      <c r="F656" s="26">
+        <v>1.47</v>
+      </c>
+      <c r="G656" s="25">
+        <v>7.96</v>
+      </c>
+      <c r="H656" s="35">
+        <v>129</v>
+      </c>
+      <c r="I656" s="25">
+        <v>1.6060000000000001</v>
+      </c>
+      <c r="J656" s="30">
+        <v>2E-3</v>
+      </c>
+      <c r="L656" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="657" spans="1:13">
+      <c r="A657" s="61">
+        <v>45723</v>
+      </c>
+      <c r="B657" t="s">
+        <v>16</v>
+      </c>
+      <c r="C657" s="35">
+        <v>11</v>
+      </c>
+      <c r="D657" s="25">
+        <v>0.15</v>
+      </c>
+      <c r="E657" s="26">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F657" s="26">
+        <v>1.5</v>
+      </c>
+      <c r="L657" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="658" spans="1:13">
+      <c r="A658" s="61">
+        <v>45723</v>
+      </c>
+      <c r="B658" t="s">
+        <v>17</v>
+      </c>
+      <c r="C658" s="35">
+        <v>0</v>
+      </c>
+      <c r="D658" s="25">
+        <v>0</v>
+      </c>
+      <c r="E658" s="26">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F658" s="26">
+        <v>2</v>
+      </c>
+      <c r="G658" s="25">
+        <v>7.83</v>
+      </c>
+      <c r="H658" s="35">
+        <v>91</v>
+      </c>
+      <c r="I658" s="25">
+        <v>0.22</v>
+      </c>
+      <c r="J658" s="30">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="L658" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="659" spans="1:13">
+      <c r="A659" s="61">
+        <v>45723</v>
+      </c>
+      <c r="B659" t="s">
+        <v>18</v>
+      </c>
+      <c r="C659" s="35">
+        <v>0</v>
+      </c>
+      <c r="D659" s="25">
+        <v>0</v>
+      </c>
+      <c r="E659" s="26">
+        <v>1.3</v>
+      </c>
+      <c r="F659" s="26">
+        <v>1.9</v>
+      </c>
+      <c r="G659" s="25">
+        <v>7.83</v>
+      </c>
+      <c r="H659" s="35">
+        <v>99</v>
+      </c>
+      <c r="I659" s="25">
+        <v>0.33600000000000002</v>
+      </c>
+      <c r="J659" s="30">
+        <v>0</v>
+      </c>
+      <c r="L659" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="660" spans="1:13">
+      <c r="A660" s="61">
+        <v>45733</v>
+      </c>
+      <c r="B660" t="s">
+        <v>17</v>
+      </c>
+      <c r="C660" s="35">
+        <v>0</v>
+      </c>
+      <c r="D660" s="25">
+        <v>7.2999999999999995E-2</v>
+      </c>
+      <c r="E660" s="26">
+        <v>1.3</v>
+      </c>
+      <c r="F660" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="H660" s="35">
+        <v>134</v>
+      </c>
+      <c r="K660" s="25">
+        <v>0</v>
+      </c>
+      <c r="L660" t="s">
+        <v>140</v>
+      </c>
+      <c r="M660" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="661" spans="1:13">
+      <c r="A661" s="61">
+        <v>45733</v>
+      </c>
+      <c r="B661" t="s">
+        <v>18</v>
+      </c>
+      <c r="C661" s="35">
+        <v>0</v>
+      </c>
+      <c r="D661" s="25">
+        <v>0.03</v>
+      </c>
+      <c r="E661" s="26">
+        <v>1.5</v>
+      </c>
+      <c r="F661" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="H661" s="35">
+        <v>178</v>
+      </c>
+      <c r="K661" s="25">
+        <v>0</v>
+      </c>
+      <c r="L661" t="s">
+        <v>140</v>
+      </c>
+      <c r="M661" t="s">
+        <v>187</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M508" xr:uid="{D6EB9ACE-4815-4899-AD47-5981DDC52F20}"/>
+  <autoFilter ref="A1:M603" xr:uid="{D6EB9ACE-4815-4899-AD47-5981DDC52F20}"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B1048576" xr:uid="{24E9CB77-83B1-4A0D-AEB9-64EF354DB25B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B569 B576:B621 B623:B1048576" xr:uid="{24E9CB77-83B1-4A0D-AEB9-64EF354DB25B}">
       <formula1>"Ocean, Mangroves, Raceway 1, Raceway 2"</formula1>
     </dataValidation>
   </dataValidations>
@@ -17640,7 +22166,7 @@
         <v>10</v>
       </c>
       <c r="K1" s="52" t="s">
-        <v>140</v>
+        <v>188</v>
       </c>
       <c r="L1" s="48" t="s">
         <v>2</v>
@@ -17664,7 +22190,7 @@
         <v>8</v>
       </c>
       <c r="S1" s="44" t="s">
-        <v>140</v>
+        <v>188</v>
       </c>
       <c r="T1" s="42" t="s">
         <v>2</v>
@@ -17694,7 +22220,7 @@
         <v>10</v>
       </c>
       <c r="AC1" s="23" t="s">
-        <v>140</v>
+        <v>188</v>
       </c>
       <c r="AD1" s="33" t="s">
         <v>2</v>
@@ -17787,7 +22313,7 @@
       <c r="AL2" s="22"/>
       <c r="AM2" s="67"/>
       <c r="AN2" s="6" t="s">
-        <v>141</v>
+        <v>189</v>
       </c>
       <c r="AO2" s="6"/>
       <c r="AP2" s="6"/>
@@ -17915,7 +22441,7 @@
       <c r="AL4" s="22"/>
       <c r="AM4" s="9"/>
       <c r="AN4" s="11" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="AO4" s="6"/>
       <c r="AP4" s="6"/>
@@ -20276,7 +24802,7 @@
       <c r="AK42" s="29"/>
       <c r="AL42" s="22"/>
       <c r="AM42" s="9" t="s">
-        <v>143</v>
+        <v>190</v>
       </c>
       <c r="AN42" s="6"/>
       <c r="AO42" s="6"/>
@@ -20307,20 +24833,20 @@
         <v>1.2</v>
       </c>
       <c r="F43" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="G43" s="60" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="H43" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="I43" s="57" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="J43" s="54"/>
       <c r="K43" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="L43" s="49">
         <v>16</v>
@@ -20338,7 +24864,7 @@
       <c r="Q43" s="49"/>
       <c r="R43" s="45"/>
       <c r="S43" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="T43" s="43"/>
       <c r="U43" s="24"/>
@@ -20360,7 +24886,7 @@
       <c r="AK43" s="29"/>
       <c r="AL43" s="22"/>
       <c r="AM43" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN43" s="6"/>
       <c r="AO43" s="6"/>
@@ -20391,20 +24917,20 @@
         <v>1.2</v>
       </c>
       <c r="F44" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="G44" s="60" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="H44" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="I44" s="57" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="J44" s="54"/>
       <c r="K44" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="L44" s="49">
         <v>14</v>
@@ -20419,12 +24945,12 @@
         <v>2.4</v>
       </c>
       <c r="P44" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="Q44" s="50"/>
       <c r="R44" s="46"/>
       <c r="S44" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="T44" s="43"/>
       <c r="U44" s="24"/>
@@ -20446,7 +24972,7 @@
       <c r="AK44" s="29"/>
       <c r="AL44" s="22"/>
       <c r="AM44" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN44" s="6"/>
       <c r="AO44" s="6"/>
@@ -20477,20 +25003,20 @@
         <v>3.5</v>
       </c>
       <c r="F45" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="G45" s="60" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="H45" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="I45" s="57" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="J45" s="54"/>
       <c r="K45" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="L45" s="49">
         <v>14</v>
@@ -20505,12 +25031,12 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="P45" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="Q45" s="50"/>
       <c r="R45" s="46"/>
       <c r="S45" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="T45" s="43"/>
       <c r="U45" s="24"/>
@@ -20532,7 +25058,7 @@
       <c r="AK45" s="29"/>
       <c r="AL45" s="22"/>
       <c r="AM45" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN45" s="6"/>
       <c r="AO45" s="6"/>
@@ -20563,20 +25089,20 @@
         <v>2.6</v>
       </c>
       <c r="F46" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="G46" s="60" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="H46" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="I46" s="57" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="J46" s="54"/>
       <c r="K46" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="L46" s="49">
         <v>12</v>
@@ -20591,12 +25117,12 @@
         <v>1.7</v>
       </c>
       <c r="P46" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="Q46" s="50"/>
       <c r="R46" s="46"/>
       <c r="S46" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="T46" s="43"/>
       <c r="U46" s="24"/>
@@ -20618,7 +25144,7 @@
       <c r="AK46" s="29"/>
       <c r="AL46" s="22"/>
       <c r="AM46" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN46" s="6"/>
       <c r="AO46" s="6"/>
@@ -20638,41 +25164,41 @@
       </c>
       <c r="B47" s="59"/>
       <c r="C47" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="D47" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="E47" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="F47" s="53">
         <v>8.1999999999999993</v>
       </c>
       <c r="G47" s="60" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="H47" s="53">
         <v>0.32</v>
       </c>
       <c r="I47" s="57" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="J47" s="54"/>
       <c r="K47" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="L47" s="50" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="M47" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="N47" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="O47" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="P47" s="45">
         <v>8.6</v>
@@ -20700,7 +25226,7 @@
       <c r="AK47" s="29"/>
       <c r="AL47" s="22"/>
       <c r="AM47" s="9" t="s">
-        <v>146</v>
+        <v>193</v>
       </c>
       <c r="AN47" s="6"/>
       <c r="AO47" s="6"/>
@@ -20720,16 +25246,16 @@
       </c>
       <c r="B48" s="59"/>
       <c r="C48" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="D48" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="E48" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="F48" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="G48" s="59">
         <v>132</v>
@@ -20742,27 +25268,27 @@
       </c>
       <c r="J48" s="53"/>
       <c r="K48" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="L48" s="50" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="M48" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="N48" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="O48" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="P48" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="Q48" s="50"/>
       <c r="R48" s="46"/>
       <c r="S48" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="T48" s="43"/>
       <c r="U48" s="24"/>
@@ -20784,7 +25310,7 @@
       <c r="AK48" s="29"/>
       <c r="AL48" s="22"/>
       <c r="AM48" s="9" t="s">
-        <v>147</v>
+        <v>194</v>
       </c>
       <c r="AN48" s="6"/>
       <c r="AO48" s="6"/>
@@ -20818,7 +25344,7 @@
         <v>8.2899999999999991</v>
       </c>
       <c r="G49" s="60" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="H49" s="53">
         <v>0.3</v>
@@ -20828,7 +25354,7 @@
       </c>
       <c r="J49" s="53"/>
       <c r="K49" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="L49" s="49">
         <v>15</v>
@@ -20843,12 +25369,12 @@
         <v>0.9</v>
       </c>
       <c r="P49" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="Q49" s="50"/>
       <c r="R49" s="46"/>
       <c r="S49" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="T49" s="43"/>
       <c r="U49" s="24"/>
@@ -20870,7 +25396,7 @@
       <c r="AK49" s="29"/>
       <c r="AL49" s="22"/>
       <c r="AM49" s="9" t="s">
-        <v>148</v>
+        <v>195</v>
       </c>
       <c r="AN49" s="6"/>
       <c r="AO49" s="6"/>
@@ -20901,20 +25427,20 @@
         <v>1.8</v>
       </c>
       <c r="F50" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="G50" s="60" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="H50" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="I50" s="57" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="J50" s="54"/>
       <c r="K50" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="L50" s="49">
         <v>17</v>
@@ -20929,12 +25455,12 @@
         <v>1.7</v>
       </c>
       <c r="P50" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="Q50" s="50"/>
       <c r="R50" s="46"/>
       <c r="S50" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="T50" s="43"/>
       <c r="U50" s="24"/>
@@ -20956,7 +25482,7 @@
       <c r="AK50" s="29"/>
       <c r="AL50" s="22"/>
       <c r="AM50" s="9" t="s">
-        <v>149</v>
+        <v>196</v>
       </c>
       <c r="AN50" s="6"/>
       <c r="AO50" s="6"/>
@@ -20987,20 +25513,20 @@
         <v>1.5</v>
       </c>
       <c r="F51" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="G51" s="60" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="H51" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="I51" s="57" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="J51" s="54"/>
       <c r="K51" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="L51" s="49">
         <v>16</v>
@@ -21015,12 +25541,12 @@
         <v>0.9</v>
       </c>
       <c r="P51" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="Q51" s="50"/>
       <c r="R51" s="46"/>
       <c r="S51" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="T51" s="43"/>
       <c r="U51" s="24"/>
@@ -21042,7 +25568,7 @@
       <c r="AK51" s="29"/>
       <c r="AL51" s="22"/>
       <c r="AM51" s="9" t="s">
-        <v>150</v>
+        <v>197</v>
       </c>
       <c r="AN51" s="6"/>
       <c r="AO51" s="6"/>
@@ -21062,13 +25588,13 @@
       </c>
       <c r="B52" s="59"/>
       <c r="C52" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="D52" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="E52" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="F52" s="53">
         <v>8.3000000000000007</v>
@@ -21084,27 +25610,27 @@
       </c>
       <c r="J52" s="53"/>
       <c r="K52" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="L52" s="50" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="M52" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="N52" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="O52" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="P52" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="Q52" s="50"/>
       <c r="R52" s="46"/>
       <c r="S52" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="T52" s="43"/>
       <c r="U52" s="24"/>
@@ -21126,7 +25652,7 @@
       <c r="AK52" s="29"/>
       <c r="AL52" s="22"/>
       <c r="AM52" s="9" t="s">
-        <v>149</v>
+        <v>196</v>
       </c>
       <c r="AN52" s="6"/>
       <c r="AO52" s="6"/>
@@ -21157,20 +25683,20 @@
         <v>2.5</v>
       </c>
       <c r="F53" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="G53" s="60" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="H53" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="I53" s="57" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="J53" s="54"/>
       <c r="K53" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="L53" s="49">
         <v>10</v>
@@ -21185,12 +25711,12 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="P53" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="Q53" s="50"/>
       <c r="R53" s="46"/>
       <c r="S53" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="T53" s="43"/>
       <c r="U53" s="24"/>
@@ -21212,7 +25738,7 @@
       <c r="AK53" s="29"/>
       <c r="AL53" s="22"/>
       <c r="AM53" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN53" s="6"/>
       <c r="AO53" s="6"/>
@@ -21246,17 +25772,17 @@
         <v>8.39</v>
       </c>
       <c r="G54" s="60" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="H54" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="I54" s="57" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="J54" s="54"/>
       <c r="K54" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="L54" s="49">
         <v>15</v>
@@ -21271,12 +25797,12 @@
         <v>1.4</v>
       </c>
       <c r="P54" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="Q54" s="50"/>
       <c r="R54" s="46"/>
       <c r="S54" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="T54" s="43"/>
       <c r="U54" s="24"/>
@@ -21298,7 +25824,7 @@
       <c r="AK54" s="29"/>
       <c r="AL54" s="22"/>
       <c r="AM54" s="9" t="s">
-        <v>149</v>
+        <v>196</v>
       </c>
       <c r="AN54" s="6"/>
       <c r="AO54" s="6"/>
@@ -21329,20 +25855,20 @@
         <v>1.6</v>
       </c>
       <c r="F55" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="G55" s="60" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="H55" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="I55" s="57" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="J55" s="54"/>
       <c r="K55" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="L55" s="49">
         <v>15</v>
@@ -21357,12 +25883,12 @@
         <v>1.2</v>
       </c>
       <c r="P55" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="Q55" s="50"/>
       <c r="R55" s="46"/>
       <c r="S55" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="T55" s="43"/>
       <c r="U55" s="24"/>
@@ -21384,7 +25910,7 @@
       <c r="AK55" s="29"/>
       <c r="AL55" s="22"/>
       <c r="AM55" s="9" t="s">
-        <v>150</v>
+        <v>197</v>
       </c>
       <c r="AN55" s="6"/>
       <c r="AO55" s="6"/>
@@ -21421,14 +25947,14 @@
         <v>75</v>
       </c>
       <c r="H56" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="I56" s="57" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="J56" s="54"/>
       <c r="K56" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="L56" s="49">
         <v>17</v>
@@ -21448,7 +25974,7 @@
       <c r="Q56" s="49"/>
       <c r="R56" s="45"/>
       <c r="S56" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="T56" s="43"/>
       <c r="U56" s="24"/>
@@ -21470,7 +25996,7 @@
       <c r="AK56" s="29"/>
       <c r="AL56" s="22"/>
       <c r="AM56" s="9" t="s">
-        <v>149</v>
+        <v>196</v>
       </c>
       <c r="AN56" s="6"/>
       <c r="AO56" s="6"/>
@@ -21501,20 +26027,20 @@
         <v>1.6</v>
       </c>
       <c r="F57" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="G57" s="60" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="H57" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="I57" s="57" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="J57" s="54"/>
       <c r="K57" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="L57" s="49">
         <v>16</v>
@@ -21529,12 +26055,12 @@
         <v>2</v>
       </c>
       <c r="P57" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="Q57" s="50"/>
       <c r="R57" s="46"/>
       <c r="S57" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="T57" s="43"/>
       <c r="U57" s="24"/>
@@ -21556,7 +26082,7 @@
       <c r="AK57" s="29"/>
       <c r="AL57" s="22"/>
       <c r="AM57" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN57" s="6"/>
       <c r="AO57" s="6"/>
@@ -21587,10 +26113,10 @@
         <v>2.5</v>
       </c>
       <c r="F58" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="G58" s="60" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="H58" s="53">
         <v>0.03</v>
@@ -21600,7 +26126,7 @@
       </c>
       <c r="J58" s="53"/>
       <c r="K58" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="L58" s="49">
         <v>16</v>
@@ -21615,12 +26141,12 @@
         <v>1.2</v>
       </c>
       <c r="P58" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="Q58" s="50"/>
       <c r="R58" s="46"/>
       <c r="S58" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="T58" s="43"/>
       <c r="U58" s="24"/>
@@ -21642,7 +26168,7 @@
       <c r="AK58" s="29"/>
       <c r="AL58" s="22"/>
       <c r="AM58" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN58" s="6"/>
       <c r="AO58" s="6"/>
@@ -21686,7 +26212,7 @@
       </c>
       <c r="J59" s="53"/>
       <c r="K59" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="L59" s="49">
         <v>17</v>
@@ -21701,12 +26227,12 @@
         <v>0.9</v>
       </c>
       <c r="P59" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="Q59" s="50"/>
       <c r="R59" s="46"/>
       <c r="S59" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="T59" s="43"/>
       <c r="U59" s="24"/>
@@ -21728,7 +26254,7 @@
       <c r="AK59" s="29"/>
       <c r="AL59" s="22"/>
       <c r="AM59" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN59" s="6"/>
       <c r="AO59" s="6"/>
@@ -21772,7 +26298,7 @@
       </c>
       <c r="J60" s="53"/>
       <c r="K60" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="L60" s="49">
         <v>22</v>
@@ -21787,12 +26313,12 @@
         <v>0.7</v>
       </c>
       <c r="P60" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="Q60" s="50"/>
       <c r="R60" s="46"/>
       <c r="S60" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="T60" s="43"/>
       <c r="U60" s="24"/>
@@ -21814,7 +26340,7 @@
       <c r="AK60" s="29"/>
       <c r="AL60" s="22"/>
       <c r="AM60" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN60" s="6"/>
       <c r="AO60" s="6"/>
@@ -21858,7 +26384,7 @@
       </c>
       <c r="J61" s="53"/>
       <c r="K61" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="L61" s="49">
         <v>18</v>
@@ -21873,12 +26399,12 @@
         <v>0.7</v>
       </c>
       <c r="P61" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="Q61" s="50"/>
       <c r="R61" s="46"/>
       <c r="S61" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="T61" s="43"/>
       <c r="U61" s="24"/>
@@ -21900,7 +26426,7 @@
       <c r="AK61" s="29"/>
       <c r="AL61" s="22"/>
       <c r="AM61" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN61" s="6"/>
       <c r="AO61" s="6"/>
@@ -21934,7 +26460,7 @@
         <v>8.6999999999999993</v>
       </c>
       <c r="G62" s="60" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="H62" s="53">
         <v>0.24</v>
@@ -21944,7 +26470,7 @@
       </c>
       <c r="J62" s="53"/>
       <c r="K62" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="L62" s="49">
         <v>22</v>
@@ -21959,12 +26485,12 @@
         <v>0.4</v>
       </c>
       <c r="P62" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="Q62" s="50"/>
       <c r="R62" s="46"/>
       <c r="S62" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="T62" s="43"/>
       <c r="U62" s="24"/>
@@ -21986,7 +26512,7 @@
       <c r="AK62" s="29"/>
       <c r="AL62" s="22"/>
       <c r="AM62" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN62" s="6"/>
       <c r="AO62" s="6"/>
@@ -22008,7 +26534,7 @@
         <v>0</v>
       </c>
       <c r="C63" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="D63" s="53">
         <v>0.7</v>
@@ -22030,13 +26556,13 @@
       </c>
       <c r="J63" s="53"/>
       <c r="K63" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="L63" s="49">
         <v>31</v>
       </c>
       <c r="M63" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="N63" s="45">
         <v>1.7</v>
@@ -22045,12 +26571,12 @@
         <v>6.6</v>
       </c>
       <c r="P63" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="Q63" s="50"/>
       <c r="R63" s="46"/>
       <c r="S63" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="T63" s="43"/>
       <c r="U63" s="24"/>
@@ -22072,7 +26598,7 @@
       <c r="AK63" s="29"/>
       <c r="AL63" s="22"/>
       <c r="AM63" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN63" s="6"/>
       <c r="AO63" s="6"/>
@@ -22116,7 +26642,7 @@
       </c>
       <c r="J64" s="53"/>
       <c r="K64" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="L64" s="49">
         <v>24</v>
@@ -22136,7 +26662,7 @@
       <c r="Q64" s="49"/>
       <c r="R64" s="45"/>
       <c r="S64" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="T64" s="43"/>
       <c r="U64" s="24"/>
@@ -22158,7 +26684,7 @@
       <c r="AK64" s="29"/>
       <c r="AL64" s="22"/>
       <c r="AM64" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN64" s="6"/>
       <c r="AO64" s="6"/>
@@ -22189,20 +26715,20 @@
         <v>1.5</v>
       </c>
       <c r="F65" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="G65" s="59">
         <v>118</v>
       </c>
       <c r="H65" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="I65" s="57" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="J65" s="54"/>
       <c r="K65" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="L65" s="49">
         <v>17</v>
@@ -22217,12 +26743,12 @@
         <v>0.9</v>
       </c>
       <c r="P65" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="Q65" s="50"/>
       <c r="R65" s="46"/>
       <c r="S65" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="T65" s="43"/>
       <c r="U65" s="24"/>
@@ -22244,7 +26770,7 @@
       <c r="AK65" s="29"/>
       <c r="AL65" s="22"/>
       <c r="AM65" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN65" s="6"/>
       <c r="AO65" s="6"/>
@@ -22288,27 +26814,27 @@
       </c>
       <c r="J66" s="53"/>
       <c r="K66" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="L66" s="50" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="M66" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="N66" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="O66" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="P66" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="Q66" s="50"/>
       <c r="R66" s="46"/>
       <c r="S66" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="T66" s="43"/>
       <c r="U66" s="24"/>
@@ -22330,7 +26856,7 @@
       <c r="AK66" s="29"/>
       <c r="AL66" s="22"/>
       <c r="AM66" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN66" s="6"/>
       <c r="AO66" s="6"/>
@@ -22374,7 +26900,7 @@
       </c>
       <c r="J67" s="53"/>
       <c r="K67" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="L67" s="49">
         <v>17</v>
@@ -22394,7 +26920,7 @@
       <c r="Q67" s="49"/>
       <c r="R67" s="45"/>
       <c r="S67" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="T67" s="43"/>
       <c r="U67" s="24"/>
@@ -22416,7 +26942,7 @@
       <c r="AK67" s="29"/>
       <c r="AL67" s="22"/>
       <c r="AM67" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN67" s="6"/>
       <c r="AO67" s="6"/>
@@ -22460,7 +26986,7 @@
       </c>
       <c r="J68" s="53"/>
       <c r="K68" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="L68" s="49">
         <v>17</v>
@@ -22480,7 +27006,7 @@
       <c r="Q68" s="49"/>
       <c r="R68" s="45"/>
       <c r="S68" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="T68" s="43"/>
       <c r="U68" s="24"/>
@@ -22502,7 +27028,7 @@
       <c r="AK68" s="29"/>
       <c r="AL68" s="22"/>
       <c r="AM68" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN68" s="6"/>
       <c r="AO68" s="6"/>
@@ -22546,7 +27072,7 @@
       </c>
       <c r="J69" s="53"/>
       <c r="K69" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="L69" s="49">
         <v>13</v>
@@ -22566,7 +27092,7 @@
       <c r="Q69" s="49"/>
       <c r="R69" s="45"/>
       <c r="S69" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="T69" s="43"/>
       <c r="U69" s="24"/>
@@ -22588,7 +27114,7 @@
       <c r="AK69" s="29"/>
       <c r="AL69" s="22"/>
       <c r="AM69" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN69" s="6"/>
       <c r="AO69" s="6"/>
@@ -22632,7 +27158,7 @@
       </c>
       <c r="J70" s="53"/>
       <c r="K70" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="L70" s="49">
         <v>15</v>
@@ -22652,7 +27178,7 @@
       <c r="Q70" s="49"/>
       <c r="R70" s="45"/>
       <c r="S70" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="T70" s="43"/>
       <c r="U70" s="24"/>
@@ -22674,7 +27200,7 @@
       <c r="AK70" s="29"/>
       <c r="AL70" s="22"/>
       <c r="AM70" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN70" s="6"/>
       <c r="AO70" s="6"/>
@@ -22718,7 +27244,7 @@
       </c>
       <c r="J71" s="53"/>
       <c r="K71" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="L71" s="49">
         <v>18</v>
@@ -22738,7 +27264,7 @@
       <c r="Q71" s="49"/>
       <c r="R71" s="45"/>
       <c r="S71" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="T71" s="43"/>
       <c r="U71" s="24"/>
@@ -22760,7 +27286,7 @@
       <c r="AK71" s="29"/>
       <c r="AL71" s="22"/>
       <c r="AM71" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN71" s="6"/>
       <c r="AO71" s="6"/>
@@ -22804,7 +27330,7 @@
       </c>
       <c r="J72" s="53"/>
       <c r="K72" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="L72" s="49">
         <v>2.7E-2</v>
@@ -22824,7 +27350,7 @@
       <c r="Q72" s="49"/>
       <c r="R72" s="45"/>
       <c r="S72" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="T72" s="43"/>
       <c r="U72" s="24"/>
@@ -22846,7 +27372,7 @@
       <c r="AK72" s="29"/>
       <c r="AL72" s="22"/>
       <c r="AM72" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN72" s="6"/>
       <c r="AO72" s="6"/>
@@ -22877,7 +27403,7 @@
         <v>1.3</v>
       </c>
       <c r="F73" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="G73" s="59">
         <v>95</v>
@@ -22890,7 +27416,7 @@
       </c>
       <c r="J73" s="53"/>
       <c r="K73" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="L73" s="49">
         <v>22</v>
@@ -22905,12 +27431,12 @@
         <v>1.9</v>
       </c>
       <c r="P73" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="Q73" s="50"/>
       <c r="R73" s="46"/>
       <c r="S73" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="T73" s="43"/>
       <c r="U73" s="24"/>
@@ -22932,7 +27458,7 @@
       <c r="AK73" s="29"/>
       <c r="AL73" s="22"/>
       <c r="AM73" s="9" t="s">
-        <v>149</v>
+        <v>196</v>
       </c>
       <c r="AN73" s="6"/>
       <c r="AO73" s="6"/>
@@ -22963,7 +27489,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="F74" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="G74" s="59">
         <v>85</v>
@@ -22976,7 +27502,7 @@
       </c>
       <c r="J74" s="53"/>
       <c r="K74" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="L74" s="49">
         <v>13</v>
@@ -22991,12 +27517,12 @@
         <v>1</v>
       </c>
       <c r="P74" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="Q74" s="50"/>
       <c r="R74" s="46"/>
       <c r="S74" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="T74" s="43"/>
       <c r="U74" s="24"/>
@@ -23018,7 +27544,7 @@
       <c r="AK74" s="29"/>
       <c r="AL74" s="22"/>
       <c r="AM74" s="9" t="s">
-        <v>151</v>
+        <v>198</v>
       </c>
       <c r="AN74" s="6"/>
       <c r="AO74" s="6"/>
@@ -23049,7 +27575,7 @@
         <v>1.7</v>
       </c>
       <c r="F75" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="G75" s="59">
         <v>126</v>
@@ -23058,31 +27584,31 @@
         <v>0.46</v>
       </c>
       <c r="I75" s="57" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="J75" s="54"/>
       <c r="K75" s="54" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="L75" s="50" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="M75" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="N75" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="O75" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="P75" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="Q75" s="50"/>
       <c r="R75" s="46"/>
       <c r="S75" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="T75" s="43"/>
       <c r="U75" s="24"/>
@@ -23104,7 +27630,7 @@
       <c r="AK75" s="29"/>
       <c r="AL75" s="22"/>
       <c r="AM75" s="9" t="s">
-        <v>152</v>
+        <v>199</v>
       </c>
       <c r="AN75" s="6"/>
       <c r="AO75" s="6"/>
@@ -23190,7 +27716,7 @@
       <c r="AK76" s="29"/>
       <c r="AL76" s="22"/>
       <c r="AM76" s="9" t="s">
-        <v>153</v>
+        <v>200</v>
       </c>
       <c r="AN76" s="6"/>
       <c r="AO76" s="6"/>
@@ -23249,12 +27775,12 @@
         <v>2.4</v>
       </c>
       <c r="P77" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="Q77" s="50"/>
       <c r="R77" s="46"/>
       <c r="S77" s="46" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="T77" s="43"/>
       <c r="U77" s="24"/>
@@ -23276,7 +27802,7 @@
       <c r="AK77" s="29"/>
       <c r="AL77" s="22"/>
       <c r="AM77" s="9" t="s">
-        <v>154</v>
+        <v>201</v>
       </c>
       <c r="AN77" s="6"/>
       <c r="AO77" s="6"/>
@@ -23362,7 +27888,7 @@
       <c r="AK78" s="29"/>
       <c r="AL78" s="22"/>
       <c r="AM78" s="9" t="s">
-        <v>155</v>
+        <v>202</v>
       </c>
       <c r="AN78" s="6"/>
       <c r="AO78" s="6"/>
@@ -23448,7 +27974,7 @@
       <c r="AK79" s="29"/>
       <c r="AL79" s="22"/>
       <c r="AM79" s="9" t="s">
-        <v>156</v>
+        <v>203</v>
       </c>
       <c r="AN79" s="6"/>
       <c r="AO79" s="6"/>
@@ -23534,7 +28060,7 @@
       <c r="AK80" s="29"/>
       <c r="AL80" s="22"/>
       <c r="AM80" s="9" t="s">
-        <v>157</v>
+        <v>204</v>
       </c>
       <c r="AN80" s="6"/>
       <c r="AO80" s="6"/>
@@ -23620,7 +28146,7 @@
       <c r="AK81" s="29"/>
       <c r="AL81" s="22"/>
       <c r="AM81" s="9" t="s">
-        <v>156</v>
+        <v>203</v>
       </c>
       <c r="AN81" s="6"/>
       <c r="AO81" s="6"/>
@@ -23706,7 +28232,7 @@
       <c r="AK82" s="29"/>
       <c r="AL82" s="22"/>
       <c r="AM82" s="9" t="s">
-        <v>157</v>
+        <v>204</v>
       </c>
       <c r="AN82" s="6"/>
       <c r="AO82" s="6"/>
@@ -23790,7 +28316,7 @@
       <c r="AK83" s="29"/>
       <c r="AL83" s="22"/>
       <c r="AM83" s="9" t="s">
-        <v>157</v>
+        <v>204</v>
       </c>
       <c r="AN83" s="6"/>
       <c r="AO83" s="6"/>
@@ -23872,7 +28398,7 @@
       <c r="AK84" s="29"/>
       <c r="AL84" s="22"/>
       <c r="AM84" s="9" t="s">
-        <v>149</v>
+        <v>196</v>
       </c>
       <c r="AN84" s="6"/>
       <c r="AO84" s="6"/>
@@ -24042,7 +28568,7 @@
       <c r="AK86" s="29"/>
       <c r="AL86" s="22"/>
       <c r="AM86" s="9" t="s">
-        <v>157</v>
+        <v>204</v>
       </c>
       <c r="AN86" s="6"/>
       <c r="AO86" s="6"/>
@@ -24214,7 +28740,7 @@
       <c r="AK88" s="29"/>
       <c r="AL88" s="22"/>
       <c r="AM88" s="9" t="s">
-        <v>157</v>
+        <v>204</v>
       </c>
       <c r="AN88" s="6"/>
       <c r="AO88" s="6"/>
@@ -24300,7 +28826,7 @@
       <c r="AK89" s="29"/>
       <c r="AL89" s="22"/>
       <c r="AM89" s="9" t="s">
-        <v>157</v>
+        <v>204</v>
       </c>
       <c r="AN89" s="6"/>
       <c r="AO89" s="6"/>
@@ -24384,7 +28910,7 @@
       <c r="AK90" s="29"/>
       <c r="AL90" s="22"/>
       <c r="AM90" s="9" t="s">
-        <v>157</v>
+        <v>204</v>
       </c>
       <c r="AN90" s="6"/>
       <c r="AO90" s="6"/>
@@ -24470,7 +28996,7 @@
       <c r="AK91" s="29"/>
       <c r="AL91" s="22"/>
       <c r="AM91" s="9" t="s">
-        <v>157</v>
+        <v>204</v>
       </c>
       <c r="AN91" s="6"/>
       <c r="AO91" s="6"/>
@@ -24542,7 +29068,7 @@
       <c r="AK92" s="29"/>
       <c r="AL92" s="22"/>
       <c r="AM92" s="9" t="s">
-        <v>149</v>
+        <v>196</v>
       </c>
       <c r="AN92" s="6"/>
       <c r="AO92" s="6"/>
@@ -24702,7 +29228,7 @@
       <c r="AK94" s="29"/>
       <c r="AL94" s="22"/>
       <c r="AM94" s="9" t="s">
-        <v>149</v>
+        <v>196</v>
       </c>
       <c r="AN94" s="6"/>
       <c r="AO94" s="6"/>
@@ -24784,7 +29310,7 @@
       <c r="AK95" s="29"/>
       <c r="AL95" s="22"/>
       <c r="AM95" s="9" t="s">
-        <v>149</v>
+        <v>196</v>
       </c>
       <c r="AN95" s="6"/>
       <c r="AO95" s="6"/>
@@ -24866,7 +29392,7 @@
       <c r="AK96" s="29"/>
       <c r="AL96" s="22"/>
       <c r="AM96" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN96" s="6"/>
       <c r="AO96" s="6"/>
@@ -24948,7 +29474,7 @@
       <c r="AK97" s="29"/>
       <c r="AL97" s="22"/>
       <c r="AM97" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN97" s="6"/>
       <c r="AO97" s="6"/>
@@ -25030,7 +29556,7 @@
       <c r="AK98" s="29"/>
       <c r="AL98" s="22"/>
       <c r="AM98" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN98" s="6"/>
       <c r="AO98" s="6"/>
@@ -25112,7 +29638,7 @@
       <c r="AK99" s="29"/>
       <c r="AL99" s="22"/>
       <c r="AM99" s="9" t="s">
-        <v>149</v>
+        <v>196</v>
       </c>
       <c r="AN99" s="6"/>
       <c r="AO99" s="6"/>
@@ -25194,7 +29720,7 @@
       <c r="AK100" s="29"/>
       <c r="AL100" s="22"/>
       <c r="AM100" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN100" s="6"/>
       <c r="AO100" s="6"/>
@@ -25276,7 +29802,7 @@
       <c r="AK101" s="29"/>
       <c r="AL101" s="22"/>
       <c r="AM101" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN101" s="6"/>
       <c r="AO101" s="6"/>
@@ -25358,7 +29884,7 @@
       <c r="AK102" s="29"/>
       <c r="AL102" s="22"/>
       <c r="AM102" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN102" s="6"/>
       <c r="AO102" s="6"/>
@@ -25440,7 +29966,7 @@
       <c r="AK103" s="29"/>
       <c r="AL103" s="22"/>
       <c r="AM103" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN103" s="6"/>
       <c r="AO103" s="6"/>
@@ -25520,7 +30046,7 @@
       <c r="AK104" s="29"/>
       <c r="AL104" s="22"/>
       <c r="AM104" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN104" s="6"/>
       <c r="AO104" s="6"/>
@@ -25602,7 +30128,7 @@
       <c r="AK105" s="29"/>
       <c r="AL105" s="22"/>
       <c r="AM105" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN105" s="6"/>
       <c r="AO105" s="6"/>
@@ -25684,7 +30210,7 @@
       <c r="AK106" s="29"/>
       <c r="AL106" s="22"/>
       <c r="AM106" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN106" s="6"/>
       <c r="AO106" s="6"/>
@@ -25764,7 +30290,7 @@
       <c r="AK107" s="29"/>
       <c r="AL107" s="22"/>
       <c r="AM107" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN107" s="6"/>
       <c r="AO107" s="6"/>
@@ -25842,7 +30368,7 @@
       <c r="AK108" s="29"/>
       <c r="AL108" s="22"/>
       <c r="AM108" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN108" s="6"/>
       <c r="AO108" s="6"/>
@@ -25920,7 +30446,7 @@
       <c r="AK109" s="29"/>
       <c r="AL109" s="22"/>
       <c r="AM109" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN109" s="6"/>
       <c r="AO109" s="6"/>
@@ -25998,7 +30524,7 @@
       <c r="AK110" s="29"/>
       <c r="AL110" s="22"/>
       <c r="AM110" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN110" s="6"/>
       <c r="AO110" s="6"/>
@@ -26076,7 +30602,7 @@
       <c r="AK111" s="29"/>
       <c r="AL111" s="22"/>
       <c r="AM111" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN111" s="6"/>
       <c r="AO111" s="6"/>
@@ -26158,7 +30684,7 @@
       <c r="AK112" s="29"/>
       <c r="AL112" s="22"/>
       <c r="AM112" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN112" s="6"/>
       <c r="AO112" s="6"/>
@@ -26232,7 +30758,7 @@
       <c r="AK113" s="29"/>
       <c r="AL113" s="22"/>
       <c r="AM113" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN113" s="6"/>
       <c r="AO113" s="6"/>
@@ -26314,7 +30840,7 @@
       <c r="AK114" s="29"/>
       <c r="AL114" s="22"/>
       <c r="AM114" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN114" s="6"/>
       <c r="AO114" s="6"/>
@@ -26390,7 +30916,7 @@
       <c r="AK115" s="29"/>
       <c r="AL115" s="22"/>
       <c r="AM115" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN115" s="6"/>
       <c r="AO115" s="6"/>
@@ -26472,7 +30998,7 @@
       <c r="AK116" s="29"/>
       <c r="AL116" s="22"/>
       <c r="AM116" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN116" s="6"/>
       <c r="AO116" s="6"/>
@@ -26552,7 +31078,7 @@
       <c r="AK117" s="29"/>
       <c r="AL117" s="22"/>
       <c r="AM117" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN117" s="6"/>
       <c r="AO117" s="6"/>
@@ -26628,7 +31154,7 @@
       <c r="AK118" s="29"/>
       <c r="AL118" s="22"/>
       <c r="AM118" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN118" s="6"/>
       <c r="AO118" s="6"/>
@@ -26710,7 +31236,7 @@
       <c r="AK119" s="29"/>
       <c r="AL119" s="22"/>
       <c r="AM119" s="9" t="s">
-        <v>158</v>
+        <v>205</v>
       </c>
       <c r="AN119" s="6"/>
       <c r="AO119" s="6"/>
@@ -26792,7 +31318,7 @@
       <c r="AK120" s="29"/>
       <c r="AL120" s="22"/>
       <c r="AM120" s="9" t="s">
-        <v>149</v>
+        <v>196</v>
       </c>
       <c r="AN120" s="6"/>
       <c r="AO120" s="6"/>
@@ -26872,7 +31398,7 @@
       <c r="AK121" s="29"/>
       <c r="AL121" s="22"/>
       <c r="AM121" s="9" t="s">
-        <v>149</v>
+        <v>196</v>
       </c>
       <c r="AN121" s="6"/>
       <c r="AO121" s="6"/>
@@ -26954,7 +31480,7 @@
       <c r="AK122" s="29"/>
       <c r="AL122" s="22"/>
       <c r="AM122" s="9" t="s">
-        <v>149</v>
+        <v>196</v>
       </c>
       <c r="AN122" s="6"/>
       <c r="AO122" s="6"/>
@@ -27036,7 +31562,7 @@
       <c r="AK123" s="29"/>
       <c r="AL123" s="22"/>
       <c r="AM123" s="9" t="s">
-        <v>149</v>
+        <v>196</v>
       </c>
       <c r="AN123" s="6"/>
       <c r="AO123" s="6"/>
@@ -27118,7 +31644,7 @@
       <c r="AK124" s="29"/>
       <c r="AL124" s="22"/>
       <c r="AM124" s="9" t="s">
-        <v>149</v>
+        <v>196</v>
       </c>
       <c r="AN124" s="6"/>
       <c r="AO124" s="6"/>
@@ -27200,7 +31726,7 @@
       <c r="AK125" s="29"/>
       <c r="AL125" s="22"/>
       <c r="AM125" s="9" t="s">
-        <v>149</v>
+        <v>196</v>
       </c>
       <c r="AN125" s="6"/>
       <c r="AO125" s="6"/>
@@ -27282,7 +31808,7 @@
       <c r="AK126" s="29"/>
       <c r="AL126" s="22"/>
       <c r="AM126" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN126" s="6"/>
       <c r="AO126" s="6"/>
@@ -27364,7 +31890,7 @@
       <c r="AK127" s="29"/>
       <c r="AL127" s="22"/>
       <c r="AM127" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN127" s="6"/>
       <c r="AO127" s="6"/>
@@ -27446,7 +31972,7 @@
       <c r="AK128" s="29"/>
       <c r="AL128" s="22"/>
       <c r="AM128" s="9" t="s">
-        <v>158</v>
+        <v>205</v>
       </c>
       <c r="AN128" s="6"/>
       <c r="AO128" s="6"/>
@@ -27538,7 +32064,7 @@
       <c r="AK129" s="29"/>
       <c r="AL129" s="22"/>
       <c r="AM129" s="9" t="s">
-        <v>158</v>
+        <v>205</v>
       </c>
       <c r="AN129" s="6"/>
       <c r="AO129" s="6"/>
@@ -27620,7 +32146,7 @@
       <c r="AK130" s="29"/>
       <c r="AL130" s="22"/>
       <c r="AM130" s="9" t="s">
-        <v>149</v>
+        <v>196</v>
       </c>
       <c r="AN130" s="6"/>
       <c r="AO130" s="6"/>
@@ -27712,7 +32238,7 @@
       <c r="AK131" s="29"/>
       <c r="AL131" s="22"/>
       <c r="AM131" s="9" t="s">
-        <v>149</v>
+        <v>196</v>
       </c>
       <c r="AN131" s="6"/>
       <c r="AO131" s="6"/>
@@ -27790,7 +32316,7 @@
       <c r="AK132" s="29"/>
       <c r="AL132" s="22"/>
       <c r="AM132" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN132" s="6"/>
       <c r="AO132" s="6"/>
@@ -27872,7 +32398,7 @@
       <c r="AK133" s="29"/>
       <c r="AL133" s="22"/>
       <c r="AM133" s="9" t="s">
-        <v>149</v>
+        <v>196</v>
       </c>
       <c r="AN133" s="6"/>
       <c r="AO133" s="6"/>
@@ -27954,7 +32480,7 @@
       <c r="AK134" s="29"/>
       <c r="AL134" s="22"/>
       <c r="AM134" s="9" t="s">
-        <v>149</v>
+        <v>196</v>
       </c>
       <c r="AN134" s="6"/>
       <c r="AO134" s="6"/>
@@ -28032,7 +32558,7 @@
       <c r="AK135" s="29"/>
       <c r="AL135" s="22"/>
       <c r="AM135" s="9" t="s">
-        <v>149</v>
+        <v>196</v>
       </c>
       <c r="AN135" s="6"/>
       <c r="AO135" s="6"/>
@@ -28110,7 +32636,7 @@
       <c r="AK136" s="29"/>
       <c r="AL136" s="22"/>
       <c r="AM136" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN136" s="6"/>
       <c r="AO136" s="6"/>
@@ -28188,7 +32714,7 @@
       <c r="AK137" s="29"/>
       <c r="AL137" s="22"/>
       <c r="AM137" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN137" s="6"/>
       <c r="AO137" s="6"/>
@@ -28258,7 +32784,7 @@
       <c r="AK138" s="29"/>
       <c r="AL138" s="22"/>
       <c r="AM138" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN138" s="6"/>
       <c r="AO138" s="6"/>
@@ -28354,7 +32880,7 @@
       <c r="AK139" s="29"/>
       <c r="AL139" s="22"/>
       <c r="AM139" s="9" t="s">
-        <v>149</v>
+        <v>196</v>
       </c>
       <c r="AN139" s="6"/>
       <c r="AO139" s="6"/>
@@ -28450,7 +32976,7 @@
       <c r="AK140" s="29"/>
       <c r="AL140" s="22"/>
       <c r="AM140" s="9" t="s">
-        <v>149</v>
+        <v>196</v>
       </c>
       <c r="AN140" s="6"/>
       <c r="AO140" s="6"/>
@@ -28542,7 +33068,7 @@
       <c r="AK141" s="29"/>
       <c r="AL141" s="22"/>
       <c r="AM141" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN141" s="6"/>
       <c r="AO141" s="6"/>
@@ -28634,7 +33160,7 @@
       <c r="AK142" s="29"/>
       <c r="AL142" s="22"/>
       <c r="AM142" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN142" s="6"/>
       <c r="AO142" s="6"/>
@@ -28730,7 +33256,7 @@
       <c r="AK143" s="29"/>
       <c r="AL143" s="22"/>
       <c r="AM143" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN143" s="6"/>
       <c r="AO143" s="6"/>
@@ -28822,7 +33348,7 @@
       <c r="AK144" s="29"/>
       <c r="AL144" s="22"/>
       <c r="AM144" s="9" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AN144" s="6"/>
       <c r="AO144" s="6"/>
@@ -28916,7 +33442,7 @@
       <c r="AK145" s="29"/>
       <c r="AL145" s="22"/>
       <c r="AM145" s="9" t="s">
-        <v>159</v>
+        <v>206</v>
       </c>
       <c r="AN145" s="6"/>
       <c r="AO145" s="6"/>
@@ -29014,7 +33540,7 @@
       <c r="AK146" s="29"/>
       <c r="AL146" s="22"/>
       <c r="AM146" s="9" t="s">
-        <v>160</v>
+        <v>207</v>
       </c>
       <c r="AN146" s="6"/>
       <c r="AO146" s="6"/>
@@ -29045,7 +33571,7 @@
         <v>1.8</v>
       </c>
       <c r="F147" s="53" t="s">
-        <v>161</v>
+        <v>208</v>
       </c>
       <c r="G147" s="59">
         <v>102</v>
@@ -29110,7 +33636,7 @@
       <c r="AK147" s="29"/>
       <c r="AL147" s="22"/>
       <c r="AM147" s="9" t="s">
-        <v>162</v>
+        <v>209</v>
       </c>
       <c r="AN147" s="6"/>
       <c r="AO147" s="6"/>
@@ -29208,7 +33734,7 @@
       <c r="AK148" s="29"/>
       <c r="AL148" s="22"/>
       <c r="AM148" s="9" t="s">
-        <v>163</v>
+        <v>210</v>
       </c>
       <c r="AN148" s="6"/>
       <c r="AO148" s="6"/>
@@ -29304,7 +33830,7 @@
       <c r="AK149" s="29"/>
       <c r="AL149" s="22"/>
       <c r="AM149" s="9" t="s">
-        <v>163</v>
+        <v>210</v>
       </c>
       <c r="AN149" s="6"/>
       <c r="AO149" s="6"/>
@@ -29400,7 +33926,7 @@
       <c r="AK150" s="29"/>
       <c r="AL150" s="22"/>
       <c r="AM150" s="9" t="s">
-        <v>163</v>
+        <v>210</v>
       </c>
       <c r="AN150" s="6"/>
       <c r="AO150" s="6"/>
@@ -29496,7 +34022,7 @@
       <c r="AK151" s="29"/>
       <c r="AL151" s="22"/>
       <c r="AM151" s="9" t="s">
-        <v>163</v>
+        <v>210</v>
       </c>
       <c r="AN151" s="6"/>
       <c r="AO151" s="6"/>
@@ -29592,7 +34118,7 @@
       <c r="AK152" s="29"/>
       <c r="AL152" s="22"/>
       <c r="AM152" s="9" t="s">
-        <v>163</v>
+        <v>210</v>
       </c>
       <c r="AN152" s="6"/>
       <c r="AO152" s="6"/>
@@ -29688,7 +34214,7 @@
       <c r="AK153" s="29"/>
       <c r="AL153" s="22"/>
       <c r="AM153" s="9" t="s">
-        <v>163</v>
+        <v>210</v>
       </c>
       <c r="AN153" s="6"/>
       <c r="AO153" s="6"/>
@@ -29780,7 +34306,7 @@
       <c r="AK154" s="29"/>
       <c r="AL154" s="22"/>
       <c r="AM154" s="9" t="s">
-        <v>164</v>
+        <v>211</v>
       </c>
       <c r="AN154" s="6"/>
       <c r="AO154" s="6"/>
@@ -29876,7 +34402,7 @@
       <c r="AK155" s="29"/>
       <c r="AL155" s="22"/>
       <c r="AM155" s="9" t="s">
-        <v>163</v>
+        <v>210</v>
       </c>
       <c r="AN155" s="6"/>
       <c r="AO155" s="6"/>
@@ -29972,7 +34498,7 @@
       <c r="AK156" s="29"/>
       <c r="AL156" s="22"/>
       <c r="AM156" s="9" t="s">
-        <v>163</v>
+        <v>210</v>
       </c>
       <c r="AN156" s="6"/>
       <c r="AO156" s="6"/>
@@ -30068,7 +34594,7 @@
       <c r="AK157" s="29"/>
       <c r="AL157" s="22"/>
       <c r="AM157" s="9" t="s">
-        <v>163</v>
+        <v>210</v>
       </c>
       <c r="AN157" s="6"/>
       <c r="AO157" s="6"/>
@@ -30164,7 +34690,7 @@
       <c r="AK158" s="29"/>
       <c r="AL158" s="22"/>
       <c r="AM158" s="9" t="s">
-        <v>163</v>
+        <v>210</v>
       </c>
       <c r="AN158" s="6"/>
       <c r="AO158" s="6"/>
@@ -30260,7 +34786,7 @@
       <c r="AK159" s="29"/>
       <c r="AL159" s="22"/>
       <c r="AM159" s="9" t="s">
-        <v>146</v>
+        <v>193</v>
       </c>
       <c r="AN159" s="6"/>
       <c r="AO159" s="6"/>
@@ -30358,7 +34884,7 @@
       <c r="AK160" s="29"/>
       <c r="AL160" s="22"/>
       <c r="AM160" s="9" t="s">
-        <v>146</v>
+        <v>193</v>
       </c>
       <c r="AN160" s="6"/>
       <c r="AO160" s="6"/>
@@ -30454,7 +34980,7 @@
       <c r="AK161" s="29"/>
       <c r="AL161" s="22"/>
       <c r="AM161" s="9" t="s">
-        <v>165</v>
+        <v>212</v>
       </c>
       <c r="AN161" s="6"/>
       <c r="AO161" s="6"/>
@@ -30550,7 +35076,7 @@
       <c r="AK162" s="29"/>
       <c r="AL162" s="22"/>
       <c r="AM162" s="9" t="s">
-        <v>166</v>
+        <v>213</v>
       </c>
       <c r="AN162" s="6"/>
       <c r="AO162" s="6"/>
@@ -30646,7 +35172,7 @@
       <c r="AK163" s="29"/>
       <c r="AL163" s="22"/>
       <c r="AM163" s="9" t="s">
-        <v>167</v>
+        <v>214</v>
       </c>
       <c r="AN163" s="6"/>
       <c r="AO163" s="6"/>
@@ -30742,7 +35268,7 @@
       <c r="AK164" s="29"/>
       <c r="AL164" s="22"/>
       <c r="AM164" s="9" t="s">
-        <v>168</v>
+        <v>215</v>
       </c>
       <c r="AN164" s="6"/>
       <c r="AO164" s="6"/>
@@ -30838,7 +35364,7 @@
       <c r="AK165" s="29"/>
       <c r="AL165" s="22"/>
       <c r="AM165" s="9" t="s">
-        <v>167</v>
+        <v>214</v>
       </c>
       <c r="AN165" s="6"/>
       <c r="AO165" s="6"/>
@@ -30930,10 +35456,10 @@
       <c r="AK166" s="29"/>
       <c r="AL166" s="22"/>
       <c r="AM166" s="9" t="s">
-        <v>167</v>
+        <v>214</v>
       </c>
       <c r="AN166" s="6" t="s">
-        <v>169</v>
+        <v>216</v>
       </c>
       <c r="AO166" s="6"/>
       <c r="AP166" s="6"/>
@@ -31028,7 +35554,7 @@
       <c r="AK167" s="29"/>
       <c r="AL167" s="22"/>
       <c r="AM167" s="9" t="s">
-        <v>170</v>
+        <v>217</v>
       </c>
       <c r="AN167" s="6"/>
       <c r="AO167" s="6"/>
@@ -31124,7 +35650,7 @@
       <c r="AK168" s="29"/>
       <c r="AL168" s="22"/>
       <c r="AM168" s="9" t="s">
-        <v>167</v>
+        <v>214</v>
       </c>
       <c r="AN168" s="6"/>
       <c r="AO168" s="6"/>
@@ -31236,7 +35762,7 @@
       </c>
       <c r="AL169" s="22"/>
       <c r="AM169" s="9" t="s">
-        <v>163</v>
+        <v>210</v>
       </c>
       <c r="AN169" s="6"/>
       <c r="AO169" s="6"/>
@@ -31348,7 +35874,7 @@
       </c>
       <c r="AL170" s="22"/>
       <c r="AM170" s="9" t="s">
-        <v>168</v>
+        <v>215</v>
       </c>
       <c r="AN170" s="6"/>
       <c r="AO170" s="6"/>
@@ -31460,7 +35986,7 @@
       </c>
       <c r="AL171" s="22"/>
       <c r="AM171" s="9" t="s">
-        <v>168</v>
+        <v>215</v>
       </c>
       <c r="AN171" s="6"/>
       <c r="AO171" s="6"/>
@@ -31572,7 +36098,7 @@
       </c>
       <c r="AL172" s="22"/>
       <c r="AM172" s="9" t="s">
-        <v>171</v>
+        <v>218</v>
       </c>
       <c r="AN172" s="6"/>
       <c r="AO172" s="6"/>
@@ -31684,7 +36210,7 @@
       </c>
       <c r="AL173" s="22"/>
       <c r="AM173" s="9" t="s">
-        <v>163</v>
+        <v>210</v>
       </c>
       <c r="AN173" s="6"/>
       <c r="AO173" s="6"/>
@@ -31796,7 +36322,7 @@
       </c>
       <c r="AL174" s="22"/>
       <c r="AM174" s="9" t="s">
-        <v>167</v>
+        <v>214</v>
       </c>
       <c r="AN174" s="6"/>
       <c r="AO174" s="6"/>
@@ -31908,7 +36434,7 @@
       </c>
       <c r="AL175" s="22"/>
       <c r="AM175" s="9" t="s">
-        <v>170</v>
+        <v>217</v>
       </c>
       <c r="AN175" s="6"/>
       <c r="AO175" s="6"/>
@@ -32020,7 +36546,7 @@
       </c>
       <c r="AL176" s="22"/>
       <c r="AM176" s="9" t="s">
-        <v>172</v>
+        <v>219</v>
       </c>
       <c r="AN176" s="6"/>
       <c r="AO176" s="6"/>
@@ -32132,7 +36658,7 @@
       </c>
       <c r="AL177" s="22"/>
       <c r="AM177" s="9" t="s">
-        <v>170</v>
+        <v>217</v>
       </c>
       <c r="AN177" s="6"/>
       <c r="AO177" s="6"/>
@@ -32244,7 +36770,7 @@
       </c>
       <c r="AL178" s="22"/>
       <c r="AM178" s="9" t="s">
-        <v>171</v>
+        <v>218</v>
       </c>
       <c r="AN178" s="6"/>
       <c r="AO178" s="6"/>
@@ -32358,7 +36884,7 @@
       </c>
       <c r="AL179" s="22"/>
       <c r="AM179" s="9" t="s">
-        <v>173</v>
+        <v>220</v>
       </c>
       <c r="AN179" s="6"/>
       <c r="AO179" s="6"/>
@@ -32470,7 +36996,7 @@
       </c>
       <c r="AL180" s="22"/>
       <c r="AM180" s="9" t="s">
-        <v>168</v>
+        <v>215</v>
       </c>
       <c r="AN180" s="6"/>
       <c r="AO180" s="6"/>
@@ -32582,7 +37108,7 @@
       </c>
       <c r="AL181" s="22"/>
       <c r="AM181" s="14" t="s">
-        <v>168</v>
+        <v>215</v>
       </c>
       <c r="AN181" s="6"/>
       <c r="AO181" s="6"/>
@@ -32690,10 +37216,10 @@
       </c>
       <c r="AL182" s="22"/>
       <c r="AM182" s="14" t="s">
-        <v>174</v>
+        <v>221</v>
       </c>
       <c r="AN182" s="15" t="s">
-        <v>175</v>
+        <v>222</v>
       </c>
       <c r="AO182" s="6"/>
       <c r="AP182" s="6"/>
@@ -32798,7 +37324,7 @@
       </c>
       <c r="AL183" s="22"/>
       <c r="AM183" s="9" t="s">
-        <v>163</v>
+        <v>210</v>
       </c>
       <c r="AN183" s="6"/>
       <c r="AO183" s="6"/>
@@ -32904,10 +37430,10 @@
       <c r="AK184" s="29"/>
       <c r="AL184" s="22"/>
       <c r="AM184" s="9" t="s">
-        <v>176</v>
+        <v>223</v>
       </c>
       <c r="AN184" s="6" t="s">
-        <v>177</v>
+        <v>224</v>
       </c>
       <c r="AO184" s="6"/>
       <c r="AP184" s="6"/>
@@ -33020,7 +37546,7 @@
       </c>
       <c r="AL185" s="22"/>
       <c r="AM185" s="9" t="s">
-        <v>178</v>
+        <v>225</v>
       </c>
       <c r="AN185" s="6"/>
       <c r="AO185" s="6"/>
@@ -33134,7 +37660,7 @@
       </c>
       <c r="AL186" s="22"/>
       <c r="AM186" s="9" t="s">
-        <v>179</v>
+        <v>226</v>
       </c>
       <c r="AN186" s="6"/>
       <c r="AO186" s="6"/>
@@ -33246,7 +37772,7 @@
       </c>
       <c r="AL187" s="22"/>
       <c r="AM187" s="9" t="s">
-        <v>176</v>
+        <v>223</v>
       </c>
       <c r="AN187" s="6"/>
       <c r="AO187" s="6"/>
@@ -33358,7 +37884,7 @@
       </c>
       <c r="AL188" s="22"/>
       <c r="AM188" s="9" t="s">
-        <v>180</v>
+        <v>227</v>
       </c>
       <c r="AN188" s="6"/>
       <c r="AO188" s="6"/>
@@ -33470,7 +37996,7 @@
       </c>
       <c r="AL189" s="22"/>
       <c r="AM189" s="9" t="s">
-        <v>181</v>
+        <v>228</v>
       </c>
       <c r="AN189" s="6"/>
       <c r="AO189" s="6"/>
@@ -33582,7 +38108,7 @@
       </c>
       <c r="AL190" s="22"/>
       <c r="AM190" s="9" t="s">
-        <v>168</v>
+        <v>215</v>
       </c>
       <c r="AN190" s="6"/>
       <c r="AO190" s="6"/>
@@ -33694,7 +38220,7 @@
       </c>
       <c r="AL191" s="22"/>
       <c r="AM191" s="9" t="s">
-        <v>172</v>
+        <v>219</v>
       </c>
       <c r="AN191" s="6"/>
       <c r="AO191" s="6"/>
@@ -33806,7 +38332,7 @@
       </c>
       <c r="AL192" s="22"/>
       <c r="AM192" s="9" t="s">
-        <v>168</v>
+        <v>215</v>
       </c>
       <c r="AN192" s="6"/>
       <c r="AO192" s="6"/>
@@ -33918,7 +38444,7 @@
       </c>
       <c r="AL193" s="22"/>
       <c r="AM193" s="9" t="s">
-        <v>181</v>
+        <v>228</v>
       </c>
       <c r="AN193" s="6"/>
       <c r="AO193" s="6"/>
@@ -34030,7 +38556,7 @@
       </c>
       <c r="AL194" s="22"/>
       <c r="AM194" s="9" t="s">
-        <v>181</v>
+        <v>228</v>
       </c>
       <c r="AN194" s="6"/>
       <c r="AO194" s="6"/>
@@ -34142,7 +38668,7 @@
       </c>
       <c r="AL195" s="22"/>
       <c r="AM195" s="9" t="s">
-        <v>181</v>
+        <v>228</v>
       </c>
       <c r="AN195" s="6"/>
       <c r="AO195" s="6"/>
@@ -34254,7 +38780,7 @@
       </c>
       <c r="AL196" s="22"/>
       <c r="AM196" s="9" t="s">
-        <v>181</v>
+        <v>228</v>
       </c>
       <c r="AN196" s="6"/>
       <c r="AO196" s="6"/>
@@ -34366,7 +38892,7 @@
       </c>
       <c r="AL197" s="22"/>
       <c r="AM197" s="9" t="s">
-        <v>181</v>
+        <v>228</v>
       </c>
       <c r="AN197" s="6"/>
       <c r="AO197" s="6"/>
@@ -34478,7 +39004,7 @@
       </c>
       <c r="AL198" s="22"/>
       <c r="AM198" s="9" t="s">
-        <v>181</v>
+        <v>228</v>
       </c>
       <c r="AN198" s="6"/>
       <c r="AO198" s="6"/>
@@ -34590,7 +39116,7 @@
       </c>
       <c r="AL199" s="22"/>
       <c r="AM199" s="9" t="s">
-        <v>181</v>
+        <v>228</v>
       </c>
       <c r="AN199" s="6"/>
       <c r="AO199" s="6"/>
@@ -34692,7 +39218,7 @@
       </c>
       <c r="AL200" s="22"/>
       <c r="AM200" s="9" t="s">
-        <v>172</v>
+        <v>219</v>
       </c>
       <c r="AN200" s="6"/>
       <c r="AO200" s="6"/>
@@ -34804,7 +39330,7 @@
       </c>
       <c r="AL201" s="22"/>
       <c r="AM201" s="9" t="s">
-        <v>181</v>
+        <v>228</v>
       </c>
       <c r="AN201" s="6"/>
       <c r="AO201" s="6"/>
@@ -34918,7 +39444,7 @@
       </c>
       <c r="AL202" s="22"/>
       <c r="AM202" s="9" t="s">
-        <v>181</v>
+        <v>228</v>
       </c>
       <c r="AN202" s="6"/>
       <c r="AO202" s="6"/>
@@ -35030,7 +39556,7 @@
       </c>
       <c r="AL203" s="22"/>
       <c r="AM203" s="9" t="s">
-        <v>181</v>
+        <v>228</v>
       </c>
       <c r="AN203" s="6"/>
       <c r="AO203" s="6"/>
@@ -35142,7 +39668,7 @@
       </c>
       <c r="AL204" s="22"/>
       <c r="AM204" s="9" t="s">
-        <v>181</v>
+        <v>228</v>
       </c>
       <c r="AN204" s="6"/>
       <c r="AO204" s="6"/>
@@ -35254,7 +39780,7 @@
       </c>
       <c r="AL205" s="22"/>
       <c r="AM205" s="9" t="s">
-        <v>168</v>
+        <v>215</v>
       </c>
       <c r="AN205" s="6"/>
       <c r="AO205" s="6"/>
@@ -35369,7 +39895,7 @@
         <v>38</v>
       </c>
       <c r="AN206" s="6" t="s">
-        <v>182</v>
+        <v>229</v>
       </c>
       <c r="AO206" s="6"/>
       <c r="AP206" s="6"/>
@@ -35483,7 +40009,7 @@
         <v>38</v>
       </c>
       <c r="AN207" s="6" t="s">
-        <v>183</v>
+        <v>230</v>
       </c>
       <c r="AO207" s="6"/>
       <c r="AP207" s="6"/>
@@ -35597,7 +40123,7 @@
         <v>38</v>
       </c>
       <c r="AN208" s="6" t="s">
-        <v>184</v>
+        <v>231</v>
       </c>
       <c r="AO208" s="6"/>
       <c r="AP208" s="6"/>
@@ -36044,7 +40570,7 @@
       </c>
       <c r="AL212" s="22"/>
       <c r="AM212" s="9" t="s">
-        <v>185</v>
+        <v>232</v>
       </c>
       <c r="AN212" s="6"/>
       <c r="AO212" s="6"/>
@@ -36271,7 +40797,7 @@
         <v>38</v>
       </c>
       <c r="AN214" s="6" t="s">
-        <v>186</v>
+        <v>233</v>
       </c>
       <c r="AO214" s="6"/>
       <c r="AP214" s="6"/>
@@ -36494,7 +41020,7 @@
       </c>
       <c r="AL216" s="22"/>
       <c r="AM216" s="9" t="s">
-        <v>187</v>
+        <v>234</v>
       </c>
       <c r="AN216" s="6"/>
       <c r="AO216" s="6"/>
@@ -36606,7 +41132,7 @@
       </c>
       <c r="AL217" s="22"/>
       <c r="AM217" s="9" t="s">
-        <v>187</v>
+        <v>234</v>
       </c>
       <c r="AN217" s="6"/>
       <c r="AO217" s="6"/>
@@ -36643,7 +41169,7 @@
         <v>134</v>
       </c>
       <c r="H218" s="53" t="s">
-        <v>188</v>
+        <v>235</v>
       </c>
       <c r="I218" s="56">
         <v>1.6E-2</v>
@@ -36685,7 +41211,7 @@
         <v>103</v>
       </c>
       <c r="Z218" s="24" t="s">
-        <v>188</v>
+        <v>235</v>
       </c>
       <c r="AA218" s="39">
         <v>2.1999999999999999E-2</v>
@@ -36711,17 +41237,17 @@
         <v>80</v>
       </c>
       <c r="AJ218" s="22" t="s">
-        <v>188</v>
+        <v>235</v>
       </c>
       <c r="AK218" s="29">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="AL218" s="22"/>
       <c r="AM218" s="9" t="s">
-        <v>189</v>
+        <v>236</v>
       </c>
       <c r="AN218" s="6" t="s">
-        <v>190</v>
+        <v>237</v>
       </c>
       <c r="AO218" s="6"/>
       <c r="AP218" s="6"/>
@@ -36745,10 +41271,10 @@
         <v>0.12</v>
       </c>
       <c r="D219" s="53" t="s">
-        <v>188</v>
+        <v>235</v>
       </c>
       <c r="E219" s="53" t="s">
-        <v>188</v>
+        <v>235</v>
       </c>
       <c r="F219" s="53">
         <v>8.11</v>
@@ -36757,7 +41283,7 @@
         <v>132</v>
       </c>
       <c r="H219" s="53" t="s">
-        <v>188</v>
+        <v>235</v>
       </c>
       <c r="I219" s="56">
         <v>5.0000000000000001E-3</v>
@@ -36771,10 +41297,10 @@
         <v>0.81</v>
       </c>
       <c r="N219" s="45" t="s">
-        <v>188</v>
+        <v>235</v>
       </c>
       <c r="O219" s="45" t="s">
-        <v>188</v>
+        <v>235</v>
       </c>
       <c r="P219" s="45"/>
       <c r="Q219" s="49"/>
@@ -36799,7 +41325,7 @@
         <v>98</v>
       </c>
       <c r="Z219" s="24" t="s">
-        <v>188</v>
+        <v>235</v>
       </c>
       <c r="AA219" s="39">
         <v>6.0000000000000001E-3</v>
@@ -36825,7 +41351,7 @@
         <v>81</v>
       </c>
       <c r="AJ219" s="22" t="s">
-        <v>188</v>
+        <v>235</v>
       </c>
       <c r="AK219" s="29">
         <v>3.0000000000000001E-3</v>
@@ -36835,7 +41361,7 @@
         <v>26</v>
       </c>
       <c r="AN219" s="6" t="s">
-        <v>191</v>
+        <v>238</v>
       </c>
       <c r="AO219" s="6"/>
       <c r="AP219" s="6"/>
@@ -37282,7 +41808,7 @@
       </c>
       <c r="AL223" s="22"/>
       <c r="AM223" s="9" t="s">
-        <v>192</v>
+        <v>239</v>
       </c>
       <c r="AN223" s="6"/>
       <c r="AO223" s="6"/>
@@ -37394,7 +41920,7 @@
       </c>
       <c r="AL224" s="22"/>
       <c r="AM224" s="9" t="s">
-        <v>193</v>
+        <v>240</v>
       </c>
       <c r="AN224" s="6"/>
       <c r="AO224" s="6"/>
@@ -37506,7 +42032,7 @@
       </c>
       <c r="AL225" s="22"/>
       <c r="AM225" s="9" t="s">
-        <v>194</v>
+        <v>241</v>
       </c>
       <c r="AN225" s="6"/>
       <c r="AO225" s="6"/>
@@ -37624,10 +42150,10 @@
       </c>
       <c r="AL226" s="22"/>
       <c r="AM226" s="9" t="s">
-        <v>193</v>
+        <v>240</v>
       </c>
       <c r="AN226" s="16" t="s">
-        <v>195</v>
+        <v>242</v>
       </c>
       <c r="AO226" s="6"/>
       <c r="AP226" s="6"/>
@@ -37850,7 +42376,7 @@
       </c>
       <c r="AL228" s="22"/>
       <c r="AM228" s="9" t="s">
-        <v>193</v>
+        <v>240</v>
       </c>
       <c r="AN228" s="6"/>
       <c r="AO228" s="6"/>
@@ -37962,7 +42488,7 @@
       </c>
       <c r="AL229" s="22"/>
       <c r="AM229" s="9" t="s">
-        <v>193</v>
+        <v>240</v>
       </c>
       <c r="AN229" s="6"/>
       <c r="AO229" s="6"/>
@@ -38078,10 +42604,10 @@
       </c>
       <c r="AL230" s="22"/>
       <c r="AM230" s="9" t="s">
-        <v>193</v>
+        <v>240</v>
       </c>
       <c r="AN230" s="6" t="s">
-        <v>196</v>
+        <v>243</v>
       </c>
       <c r="AO230" s="6"/>
       <c r="AP230" s="6"/>
@@ -38304,7 +42830,7 @@
       </c>
       <c r="AL232" s="22"/>
       <c r="AM232" s="9" t="s">
-        <v>193</v>
+        <v>240</v>
       </c>
       <c r="AN232" s="6"/>
       <c r="AO232" s="6"/>
@@ -38416,10 +42942,10 @@
       </c>
       <c r="AL233" s="22"/>
       <c r="AM233" s="9" t="s">
-        <v>193</v>
+        <v>240</v>
       </c>
       <c r="AN233" s="6" t="s">
-        <v>197</v>
+        <v>244</v>
       </c>
       <c r="AO233" s="6"/>
       <c r="AP233" s="6"/>
@@ -38526,10 +43052,10 @@
       </c>
       <c r="AL234" s="22"/>
       <c r="AM234" s="9" t="s">
-        <v>198</v>
+        <v>245</v>
       </c>
       <c r="AN234" s="6" t="s">
-        <v>199</v>
+        <v>246</v>
       </c>
       <c r="AO234" s="6"/>
       <c r="AP234" s="6"/>
@@ -38640,10 +43166,10 @@
       </c>
       <c r="AL235" s="22"/>
       <c r="AM235" s="9" t="s">
-        <v>200</v>
+        <v>247</v>
       </c>
       <c r="AN235" s="6" t="s">
-        <v>201</v>
+        <v>248</v>
       </c>
       <c r="AO235" s="6"/>
       <c r="AP235" s="6"/>
@@ -38754,7 +43280,7 @@
       </c>
       <c r="AL236" s="22"/>
       <c r="AM236" s="9" t="s">
-        <v>200</v>
+        <v>247</v>
       </c>
       <c r="AN236" s="6"/>
       <c r="AO236" s="6"/>
@@ -38854,10 +43380,10 @@
       </c>
       <c r="AL237" s="22"/>
       <c r="AM237" s="9" t="s">
-        <v>202</v>
+        <v>249</v>
       </c>
       <c r="AN237" s="6" t="s">
-        <v>203</v>
+        <v>250</v>
       </c>
       <c r="AO237" s="6"/>
       <c r="AP237" s="6"/>
@@ -38946,10 +43472,10 @@
       </c>
       <c r="AL238" s="22"/>
       <c r="AM238" s="9" t="s">
-        <v>204</v>
+        <v>251</v>
       </c>
       <c r="AN238" s="6" t="s">
-        <v>205</v>
+        <v>252</v>
       </c>
       <c r="AO238" s="6"/>
       <c r="AP238" s="6"/>
@@ -39036,10 +43562,10 @@
       </c>
       <c r="AL239" s="22"/>
       <c r="AM239" s="9" t="s">
-        <v>206</v>
+        <v>253</v>
       </c>
       <c r="AN239" s="6" t="s">
-        <v>207</v>
+        <v>254</v>
       </c>
       <c r="AO239" s="6"/>
       <c r="AP239" s="6"/>
@@ -39126,10 +43652,10 @@
       </c>
       <c r="AL240" s="22"/>
       <c r="AM240" s="9" t="s">
-        <v>206</v>
+        <v>253</v>
       </c>
       <c r="AN240" s="6" t="s">
-        <v>208</v>
+        <v>255</v>
       </c>
       <c r="AO240" s="6"/>
       <c r="AP240" s="6"/>
@@ -39224,10 +43750,10 @@
       </c>
       <c r="AL241" s="22"/>
       <c r="AM241" s="9" t="s">
-        <v>209</v>
+        <v>256</v>
       </c>
       <c r="AN241" s="6" t="s">
-        <v>210</v>
+        <v>257</v>
       </c>
       <c r="AO241" s="6"/>
       <c r="AP241" s="6"/>
@@ -39342,10 +43868,10 @@
       </c>
       <c r="AL242" s="22"/>
       <c r="AM242" s="9" t="s">
-        <v>206</v>
+        <v>253</v>
       </c>
       <c r="AN242" s="6" t="s">
-        <v>211</v>
+        <v>258</v>
       </c>
       <c r="AO242" s="6"/>
       <c r="AP242" s="6"/>
@@ -39456,10 +43982,10 @@
       </c>
       <c r="AL243" s="22"/>
       <c r="AM243" s="9" t="s">
-        <v>206</v>
+        <v>253</v>
       </c>
       <c r="AN243" s="6" t="s">
-        <v>212</v>
+        <v>259</v>
       </c>
       <c r="AO243" s="6"/>
       <c r="AP243" s="6"/>
@@ -39570,7 +44096,7 @@
       </c>
       <c r="AL244" s="22"/>
       <c r="AM244" s="9" t="s">
-        <v>213</v>
+        <v>260</v>
       </c>
       <c r="AN244" s="6"/>
       <c r="AO244" s="6"/>
@@ -39686,7 +44212,7 @@
       </c>
       <c r="AL245" s="22"/>
       <c r="AM245" s="9" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
       <c r="AN245" s="6"/>
       <c r="AO245" s="6"/>
@@ -39913,7 +44439,7 @@
         <v>38</v>
       </c>
       <c r="AN247" s="6" t="s">
-        <v>215</v>
+        <v>262</v>
       </c>
       <c r="AO247" s="6"/>
       <c r="AP247" s="6"/>
@@ -40024,7 +44550,7 @@
       </c>
       <c r="AL248" s="22"/>
       <c r="AM248" s="9" t="s">
-        <v>216</v>
+        <v>263</v>
       </c>
       <c r="AN248" s="6"/>
       <c r="AO248" s="6"/>
@@ -40715,7 +45241,7 @@
         <v>2</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>217</v>
+        <v>264</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>4</v>
@@ -40736,13 +45262,13 @@
         <v>9</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>140</v>
+        <v>188</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>217</v>
+        <v>264</v>
       </c>
       <c r="M1" s="3" t="s">
         <v>4</v>
@@ -40760,13 +45286,13 @@
         <v>8</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>140</v>
+        <v>188</v>
       </c>
       <c r="S1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>217</v>
+        <v>264</v>
       </c>
       <c r="U1" s="4" t="s">
         <v>4</v>
@@ -40787,13 +45313,13 @@
         <v>9</v>
       </c>
       <c r="AA1" s="4" t="s">
-        <v>140</v>
+        <v>188</v>
       </c>
       <c r="AB1" s="5" t="s">
         <v>2</v>
       </c>
       <c r="AC1" s="5" t="s">
-        <v>217</v>
+        <v>264</v>
       </c>
       <c r="AD1" s="5" t="s">
         <v>4</v>
@@ -40816,12 +45342,12 @@
     </row>
     <row r="2" spans="1:46">
       <c r="A2" t="s">
-        <v>218</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:46" s="21" customFormat="1" ht="27.75">
       <c r="A3" s="19" t="s">
-        <v>219</v>
+        <v>266</v>
       </c>
       <c r="B3" s="20">
         <f>AVERAGE('Pre-formatted Data'!B3:B235)</f>
@@ -40969,7 +45495,7 @@
     </row>
     <row r="4" spans="1:46" s="21" customFormat="1">
       <c r="A4" s="19" t="s">
-        <v>220</v>
+        <v>267</v>
       </c>
       <c r="B4" s="20">
         <f>AVERAGE('Pre-formatted Data'!B108:B160)</f>
@@ -41082,7 +45608,7 @@
     </row>
     <row r="5" spans="1:46" s="21" customFormat="1">
       <c r="A5" s="19" t="s">
-        <v>221</v>
+        <v>268</v>
       </c>
       <c r="B5" s="20">
         <f>AVERAGE('Pre-formatted Data'!B161:B212)</f>
@@ -41219,7 +45745,7 @@
     </row>
     <row r="6" spans="1:46" s="17" customFormat="1" ht="27.75">
       <c r="A6" s="18" t="s">
-        <v>222</v>
+        <v>269</v>
       </c>
       <c r="B6" s="69">
         <f>AVERAGE('Pre-formatted Data'!B213:B235)</f>
